--- a/.claude/skills/carf-peer-support-accreditation/providers/example-peer-agency/output/05_Self_Study_Checklist.xlsx
+++ b/.claude/skills/carf-peer-support-accreditation/providers/example-peer-agency/output/05_Self_Study_Checklist.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interview Prep" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Self-Study'!$A$1:$L$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Self-Study'!$A$1:$L$150</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L146"/>
+  <dimension ref="A1:L150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -781,19 +781,19 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Corporate Compliance Plan</t>
+          <t>1A-07 Document Control, Version Management and Implementation</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Written plan</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Board of Directors</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -823,7 +823,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Cultural Competency and Diversity Plan</t>
+          <t>Corporate Compliance Plan</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -835,7 +835,7 @@
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Board of Directors</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -865,19 +865,19 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Code of Ethics Attestation</t>
+          <t>Cultural Competency and Diversity Plan</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Written plan</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Every employee, contractor, student, intern, volunteer, board member</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -907,7 +907,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Conflict of Interest Disclosure</t>
+          <t>Code of Ethics Attestation</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -919,7 +919,7 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Board members, leadership, anyone involved in purchasing, hiring, or referral decisions</t>
+          <t>Every employee, contractor, student, intern, volunteer, board member</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -934,34 +934,34 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1.B</t>
+          <t>1.A</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Leadership</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>If the organization has a governing board, the board has written duties, meets, keeps minutes, evaluates the CEO, evaluates itself, and manages conflicts of interest. A sole-owner agency documents who performs these governance functions instead.</t>
+          <t>Leadership is identified, accountable, and ethical. There is a written code of ethics, a way to raise concerns without retaliation, a corporate compliance program, and evidence that leadership considers cultural competency and the needs of the people served when making decisions.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1B-01 Governance</t>
+          <t>Conflict of Interest Disclosure</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Board of Directors</t>
+          <t>Board members, leadership, anyone involved in purchasing, hiring, or referral decisions</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -976,22 +976,22 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1.B</t>
+          <t>1.A</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Leadership</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>If the organization has a governing board, the board has written duties, meets, keeps minutes, evaluates the CEO, evaluates itself, and manages conflicts of interest. A sole-owner agency documents who performs these governance functions instead.</t>
+          <t>Leadership is identified, accountable, and ethical. There is a written code of ethics, a way to raise concerns without retaliation, a corporate compliance program, and evidence that leadership considers cultural competency and the needs of the people served when making decisions.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Governing Body Meeting Minutes</t>
+          <t>Master Document Register</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Board of Directors</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1018,22 +1018,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1.B</t>
+          <t>1.A</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Leadership</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>If the organization has a governing board, the board has written duties, meets, keeps minutes, evaluates the CEO, evaluates itself, and manages conflicts of interest. A sole-owner agency documents who performs these governance functions instead.</t>
+          <t>Leadership is identified, accountable, and ethical. There is a written code of ethics, a way to raise concerns without retaliation, a corporate compliance program, and evidence that leadership considers cultural competency and the needs of the people served when making decisions.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Governing Body Self-Assessment</t>
+          <t>Document Rollout and Implementation Record</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1045,7 +1045,7 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Each member of Board of Directors</t>
+          <t>The process owner</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1060,22 +1060,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1.B</t>
+          <t>1.A</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Leadership</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>If the organization has a governing board, the board has written duties, meets, keeps minutes, evaluates the CEO, evaluates itself, and manages conflicts of interest. A sole-owner agency documents who performs these governance functions instead.</t>
+          <t>Leadership is identified, accountable, and ethical. There is a written code of ethics, a way to raise concerns without retaliation, a corporate compliance program, and evidence that leadership considers cultural competency and the needs of the people served when making decisions.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Annual Evaluation of the Chief Executive Officer</t>
+          <t>Implementation Tracer Record</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1087,7 +1087,7 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Board of Directors</t>
+          <t>[FILL IN: Quality Improvement Coordinator] or a reviewer who does not own the process</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1102,22 +1102,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1.C</t>
+          <t>1.B</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Strategic Integrated Planning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>A written strategic plan exists that was built from real inputs: what is happening in the environment, what stakeholders expect, financial reality, technology, workforce, and risk. It is reviewed at least annually and the review is documented.</t>
+          <t>If the organization has a governing board, the board has written duties, meets, keeps minutes, evaluates the CEO, evaluates itself, and manages conflicts of interest. A sole-owner agency documents who performs these governance functions instead.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1C-01 Strategic Integrated Planning</t>
+          <t>1B-01 Governance</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Board of Directors</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1144,27 +1144,27 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1.C</t>
+          <t>1.B</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Strategic Integrated Planning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>A written strategic plan exists that was built from real inputs: what is happening in the environment, what stakeholders expect, financial reality, technology, workforce, and risk. It is reviewed at least annually and the review is documented.</t>
+          <t>If the organization has a governing board, the board has written duties, meets, keeps minutes, evaluates the CEO, evaluates itself, and manages conflicts of interest. A sole-owner agency documents who performs these governance functions instead.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Strategic Plan</t>
+          <t>Governing Body Meeting Minutes</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Written plan</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
@@ -1186,22 +1186,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1.C</t>
+          <t>1.B</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Strategic Integrated Planning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>A written strategic plan exists that was built from real inputs: what is happening in the environment, what stakeholders expect, financial reality, technology, workforce, and risk. It is reviewed at least annually and the review is documented.</t>
+          <t>If the organization has a governing board, the board has written duties, meets, keeps minutes, evaluates the CEO, evaluates itself, and manages conflicts of interest. A sole-owner agency documents who performs these governance functions instead.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Environmental Scan Worksheet</t>
+          <t>Governing Body Self-Assessment</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>Each member of Board of Directors</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1228,34 +1228,34 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1.D</t>
+          <t>1.B</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Input from Persons Served and Other Stakeholders</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>The organization systematically collects input from the people it serves and from other stakeholders (families, referral sources, payers, staff, community partners), analyzes it at least annually, acts on it, and reports the results back to those stakeholders.</t>
+          <t>If the organization has a governing board, the board has written duties, meets, keeps minutes, evaluates the CEO, evaluates itself, and manages conflicts of interest. A sole-owner agency documents who performs these governance functions instead.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1D-01 Input from Persons Served and Other Stakeholders</t>
+          <t>Annual Evaluation of the Chief Executive Officer</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>Board of Directors</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1270,34 +1270,34 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1.D</t>
+          <t>1.C</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Input from Persons Served and Other Stakeholders</t>
+          <t>Strategic Integrated Planning</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>The organization systematically collects input from the people it serves and from other stakeholders (families, referral sources, payers, staff, community partners), analyzes it at least annually, acts on it, and reports the results back to those stakeholders.</t>
+          <t>A written strategic plan exists that was built from real inputs: what is happening in the environment, what stakeholders expect, financial reality, technology, workforce, and risk. It is reviewed at least annually and the review is documented.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Satisfaction Survey — Persons Served</t>
+          <t>1C-01 Strategic Integrated Planning</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Every person served</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1312,34 +1312,34 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1.D</t>
+          <t>1.C</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Input from Persons Served and Other Stakeholders</t>
+          <t>Strategic Integrated Planning</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>The organization systematically collects input from the people it serves and from other stakeholders (families, referral sources, payers, staff, community partners), analyzes it at least annually, acts on it, and reports the results back to those stakeholders.</t>
+          <t>A written strategic plan exists that was built from real inputs: what is happening in the environment, what stakeholders expect, financial reality, technology, workforce, and risk. It is reviewed at least annually and the review is documented.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Satisfaction Survey — Other Stakeholders</t>
+          <t>Strategic Plan</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Written plan</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Referral sources, payers, community partners, families (with consent), personnel</t>
+          <t>Board of Directors</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1354,22 +1354,22 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1.D</t>
+          <t>1.C</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Input from Persons Served and Other Stakeholders</t>
+          <t>Strategic Integrated Planning</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>The organization systematically collects input from the people it serves and from other stakeholders (families, referral sources, payers, staff, community partners), analyzes it at least annually, acts on it, and reports the results back to those stakeholders.</t>
+          <t>A written strategic plan exists that was built from real inputs: what is happening in the environment, what stakeholders expect, financial reality, technology, workforce, and risk. It is reviewed at least annually and the review is documented.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Annual Input Analysis Report</t>
+          <t>Environmental Scan Worksheet</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>Leadership</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1396,22 +1396,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>1.E</t>
+          <t>1.D</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Legal Requirements</t>
+          <t>Input from Persons Served and Other Stakeholders</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>The organization knows and follows the laws, regulations, licensure and contract obligations that apply to it, and there is a written process for staying current and for reviewing contracts before signing.</t>
+          <t>The organization systematically collects input from the people it serves and from other stakeholders (families, referral sources, payers, staff, community partners), analyzes it at least annually, acts on it, and reports the results back to those stakeholders.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1E-01 Legal and Regulatory Compliance</t>
+          <t>1D-01 Input from Persons Served and Other Stakeholders</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Compliance Officer]</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1438,22 +1438,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>1.E</t>
+          <t>1.D</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Legal Requirements</t>
+          <t>Input from Persons Served and Other Stakeholders</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>The organization knows and follows the laws, regulations, licensure and contract obligations that apply to it, and there is a written process for staying current and for reviewing contracts before signing.</t>
+          <t>The organization systematically collects input from the people it serves and from other stakeholders (families, referral sources, payers, staff, community partners), analyzes it at least annually, acts on it, and reports the results back to those stakeholders.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Obligations Register</t>
+          <t>Satisfaction Survey — Persons Served</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Compliance Officer]</t>
+          <t>Every person served</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1480,34 +1480,34 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1.F</t>
+          <t>1.D</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Financial Planning and Management</t>
+          <t>Input from Persons Served and Other Stakeholders</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>There is an annual budget built on reasonable assumptions, actual results are compared to budget regularly, there are written internal controls (separation of duties, approval limits), fees are documented, and an external financial review is obtained.</t>
+          <t>The organization systematically collects input from the people it serves and from other stakeholders (families, referral sources, payers, staff, community partners), analyzes it at least annually, acts on it, and reports the results back to those stakeholders.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1F-01 Financial Planning and Budgeting</t>
+          <t>Satisfaction Survey — Other Stakeholders</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Referral sources, payers, community partners, families (with consent), personnel</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1522,34 +1522,34 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1.F</t>
+          <t>1.D</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Financial Planning and Management</t>
+          <t>Input from Persons Served and Other Stakeholders</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>There is an annual budget built on reasonable assumptions, actual results are compared to budget regularly, there are written internal controls (separation of duties, approval limits), fees are documented, and an external financial review is obtained.</t>
+          <t>The organization systematically collects input from the people it serves and from other stakeholders (families, referral sources, payers, staff, community partners), analyzes it at least annually, acts on it, and reports the results back to those stakeholders.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1F-02 Internal Financial Controls, Fees, and Billing Integrity</t>
+          <t>Annual Input Analysis Report</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1564,34 +1564,34 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1.F</t>
+          <t>1.E</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Financial Planning and Management</t>
+          <t>Legal Requirements</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>There is an annual budget built on reasonable assumptions, actual results are compared to budget regularly, there are written internal controls (separation of duties, approval limits), fees are documented, and an external financial review is obtained.</t>
+          <t>The organization knows and follows the laws, regulations, licensure and contract obligations that apply to it, and there is a written process for staying current and for reviewing contracts before signing.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Financial Plan and Budget Narrative</t>
+          <t>1E-01 Legal and Regulatory Compliance</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Written plan</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Board of Directors</t>
+          <t>[FILL IN: Compliance Officer]</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1606,22 +1606,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1.F</t>
+          <t>1.E</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Financial Planning and Management</t>
+          <t>Legal Requirements</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>There is an annual budget built on reasonable assumptions, actual results are compared to budget regularly, there are written internal controls (separation of duties, approval limits), fees are documented, and an external financial review is obtained.</t>
+          <t>The organization knows and follows the laws, regulations, licensure and contract obligations that apply to it, and there is a written process for staying current and for reviewing contracts before signing.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Monthly Budget-to-Actual Variance Review</t>
+          <t>Regulatory Obligations Register</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>[FILL IN: Compliance Officer]</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1648,22 +1648,22 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1.G</t>
+          <t>1.F</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Financial Planning and Management</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>There is a written risk management plan that names the organization's actual risks (financial, clinical, reputational, staffing, technology, community-based service delivery), what is being done about each, what insurance is carried, and when it was last reviewed.</t>
+          <t>There is an annual budget built on reasonable assumptions, actual results are compared to budget regularly, there are written internal controls (separation of duties, approval limits), fees are documented, and an external financial review is obtained.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1G-01 Risk Management</t>
+          <t>1F-01 Financial Planning and Budgeting</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1690,27 +1690,27 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1.G</t>
+          <t>1.F</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Financial Planning and Management</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>There is a written risk management plan that names the organization's actual risks (financial, clinical, reputational, staffing, technology, community-based service delivery), what is being done about each, what insurance is carried, and when it was last reviewed.</t>
+          <t>There is an annual budget built on reasonable assumptions, actual results are compared to budget regularly, there are written internal controls (separation of duties, approval limits), fees are documented, and an external financial review is obtained.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Risk Management Plan</t>
+          <t>1F-02 Internal Financial Controls, Fees, and Billing Integrity</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Written plan</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
@@ -1732,34 +1732,34 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>1.G</t>
+          <t>1.F</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Financial Planning and Management</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>There is a written risk management plan that names the organization's actual risks (financial, clinical, reputational, staffing, technology, community-based service delivery), what is being done about each, what insurance is carried, and when it was last reviewed.</t>
+          <t>There is an annual budget built on reasonable assumptions, actual results are compared to budget regularly, there are written internal controls (separation of duties, approval limits), fees are documented, and an external financial review is obtained.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Risk Register</t>
+          <t>Financial Plan and Budget Narrative</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Written plan</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Board of Directors</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -1774,34 +1774,34 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>1.H</t>
+          <t>1.F</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Health and Safety</t>
+          <t>Financial Planning and Management</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Written emergency procedures for every foreseeable emergency; drills that are actually run, documented, and critiqued; documented safety inspections; critical incident reporting and analysis; infection control; first aid and emergency training; and safety procedures for staff working alone in the community or in someone's home.</t>
+          <t>There is an annual budget built on reasonable assumptions, actual results are compared to budget regularly, there are written internal controls (separation of duties, approval limits), fees are documented, and an external financial review is obtained.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1H-01 Health and Safety Management</t>
+          <t>Monthly Budget-to-Actual Variance Review</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Safety Officer]</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -1816,22 +1816,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>1.H</t>
+          <t>1.G</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Health and Safety</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Written emergency procedures for every foreseeable emergency; drills that are actually run, documented, and critiqued; documented safety inspections; critical incident reporting and analysis; infection control; first aid and emergency training; and safety procedures for staff working alone in the community or in someone's home.</t>
+          <t>There is a written risk management plan that names the organization's actual risks (financial, clinical, reputational, staffing, technology, community-based service delivery), what is being done about each, what insurance is carried, and when it was last reviewed.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1H-02 Emergency Procedures and Drills</t>
+          <t>1G-01 Risk Management</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Safety Officer]</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -1858,34 +1858,34 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>1.H</t>
+          <t>1.G</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Health and Safety</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Written emergency procedures for every foreseeable emergency; drills that are actually run, documented, and critiqued; documented safety inspections; critical incident reporting and analysis; infection control; first aid and emergency training; and safety procedures for staff working alone in the community or in someone's home.</t>
+          <t>There is a written risk management plan that names the organization's actual risks (financial, clinical, reputational, staffing, technology, community-based service delivery), what is being done about each, what insurance is carried, and when it was last reviewed.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1H-03 Critical Incident Reporting and Analysis</t>
+          <t>Risk Management Plan</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Written plan</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Safety Officer]</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -1900,34 +1900,34 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1.H</t>
+          <t>1.G</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Health and Safety</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Written emergency procedures for every foreseeable emergency; drills that are actually run, documented, and critiqued; documented safety inspections; critical incident reporting and analysis; infection control; first aid and emergency training; and safety procedures for staff working alone in the community or in someone's home.</t>
+          <t>There is a written risk management plan that names the organization's actual risks (financial, clinical, reputational, staffing, technology, community-based service delivery), what is being done about each, what insurance is carried, and when it was last reviewed.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1H-04 Infection Prevention and Control</t>
+          <t>Risk Register</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Safety Officer]</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1H-05 Community, Home Visit, and Lone Worker Safety</t>
+          <t>1H-01 Health and Safety Management</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Safety Officer]</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -1999,12 +1999,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Health and Safety Plan</t>
+          <t>1H-02 Emergency Procedures and Drills</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Written plan</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
@@ -2041,19 +2041,19 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Business Continuity and Emergency Operations Plan</t>
+          <t>1H-03 Critical Incident Reporting and Analysis</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Written plan</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>[FILL IN: Safety Officer]</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Site Safety Inspection Checklist</t>
+          <t>1H-04 Infection Prevention and Control</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
@@ -2125,19 +2125,19 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Emergency Drill Log</t>
+          <t>1H-05 Community, Home Visit, and Lone Worker Safety</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Safety Officer]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2167,19 +2167,19 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Critical Incident Report</t>
+          <t>Health and Safety Plan</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Written plan</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>The staff member involved, reviewed by [FILL IN: Safety Officer]</t>
+          <t>[FILL IN: Safety Officer]</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2209,19 +2209,19 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Quarterly Incident Analysis Summary</t>
+          <t>Business Continuity and Emergency Operations Plan</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Written plan</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Safety Officer]</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Community and Home Visit Safety Plan</t>
+          <t>Site Safety Inspection Checklist</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Peer Support Specialist + Supervisor</t>
+          <t>[FILL IN: Safety Officer]</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Vehicle Inspection Log</t>
+          <t>Emergency Drill Log</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Driver or [FILL IN: Safety Officer]</t>
+          <t>[FILL IN: Safety Officer]</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2320,34 +2320,34 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>1.I</t>
+          <t>1.H</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Health and Safety</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Written job descriptions; verification of credentials before hire (including the state peer credential); background checks; documented orientation; competency-based training with documented competency, not just attendance; regular documented supervision; annual performance appraisal; and a documented look at workforce needs and succession.</t>
+          <t>Written emergency procedures for every foreseeable emergency; drills that are actually run, documented, and critiqued; documented safety inspections; critical incident reporting and analysis; infection control; first aid and emergency training; and safety procedures for staff working alone in the community or in someone's home.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>1I-01 Recruitment, Verification, and Hiring</t>
+          <t>Critical Incident Report</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>The staff member involved, reviewed by [FILL IN: Safety Officer]</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2362,34 +2362,34 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>1.I</t>
+          <t>1.H</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Health and Safety</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Written job descriptions; verification of credentials before hire (including the state peer credential); background checks; documented orientation; competency-based training with documented competency, not just attendance; regular documented supervision; annual performance appraisal; and a documented look at workforce needs and succession.</t>
+          <t>Written emergency procedures for every foreseeable emergency; drills that are actually run, documented, and critiqued; documented safety inspections; critical incident reporting and analysis; infection control; first aid and emergency training; and safety procedures for staff working alone in the community or in someone's home.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1I-02 Orientation and Training</t>
+          <t>Quarterly Incident Analysis Summary</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Safety Officer]</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2404,34 +2404,34 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>1.I</t>
+          <t>1.H</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Health and Safety</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Written job descriptions; verification of credentials before hire (including the state peer credential); background checks; documented orientation; competency-based training with documented competency, not just attendance; regular documented supervision; annual performance appraisal; and a documented look at workforce needs and succession.</t>
+          <t>Written emergency procedures for every foreseeable emergency; drills that are actually run, documented, and critiqued; documented safety inspections; critical incident reporting and analysis; infection control; first aid and emergency training; and safety procedures for staff working alone in the community or in someone's home.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1I-03 Competency Assessment</t>
+          <t>Community and Home Visit Safety Plan</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Supervisor of the peer workforce]</t>
+          <t>Peer Support Specialist + Supervisor</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2446,34 +2446,34 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>1.I</t>
+          <t>1.H</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Health and Safety</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Written job descriptions; verification of credentials before hire (including the state peer credential); background checks; documented orientation; competency-based training with documented competency, not just attendance; regular documented supervision; annual performance appraisal; and a documented look at workforce needs and succession.</t>
+          <t>Written emergency procedures for every foreseeable emergency; drills that are actually run, documented, and critiqued; documented safety inspections; critical incident reporting and analysis; infection control; first aid and emergency training; and safety procedures for staff working alone in the community or in someone's home.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1I-04 Supervision</t>
+          <t>Vehicle Inspection Log</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Supervisor of the peer workforce]</t>
+          <t>Driver or [FILL IN: Safety Officer]</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>1I-05 Performance Appraisal, Workforce Planning, and Personnel Records</t>
+          <t>1I-01 Recruitment, Verification, and Hiring</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2545,19 +2545,19 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Workforce Development and Succession Plan</t>
+          <t>1I-02 Orientation and Training</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Written plan</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2587,19 +2587,19 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Job Description — Peer Support Specialist</t>
+          <t>1I-03 Competency Assessment</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Employee and supervisor sign at hire and at revision</t>
+          <t>[FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -2629,19 +2629,19 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Job Description — Peer Supervisor</t>
+          <t>1I-04 Supervision</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Employee and supervisor sign at hire and at revision</t>
+          <t>[FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -2671,19 +2671,19 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Job Description — Program Director</t>
+          <t>1I-05 Performance Appraisal, Workforce Planning, and Personnel Records</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Employee and supervisor sign at hire and at revision</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -2713,19 +2713,19 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>New Personnel Orientation Checklist</t>
+          <t>Workforce Development and Succession Plan</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Written plan</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>New employee, contractor, student, intern, volunteer</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Competency Assessment — Peer Support Specialist</t>
+          <t>Job Description — Peer Support Specialist</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2767,7 +2767,7 @@
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Supervisor of the peer workforce]</t>
+          <t>Employee and supervisor sign at hire and at revision</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Supervision Note</t>
+          <t>Job Description — Peer Supervisor</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Supervisor of the peer workforce] and supervisee</t>
+          <t>Employee and supervisor sign at hire and at revision</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Annual Performance Appraisal</t>
+          <t>Job Description — Program Director</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Supervisor and employee</t>
+          <t>Employee and supervisor sign at hire and at revision</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Credential and Background Verification Log</t>
+          <t>New Personnel Orientation Checklist</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2893,7 +2893,7 @@
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer or designee</t>
+          <t>New employee, contractor, student, intern, volunteer</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Individual Training Log</t>
+          <t>Competency Assessment — Peer Support Specialist</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2935,7 +2935,7 @@
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Personnel File Checklist</t>
+          <t>Supervision Note</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2977,7 +2977,7 @@
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer or designee</t>
+          <t>[FILL IN: Supervisor of the peer workforce] and supervisee</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -2992,34 +2992,34 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>1.I</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>A written technology and systems plan covering the systems in use, who may access what, how data is backed up and tested, what happens when the system is down, and how confidentiality is protected. If information and communication technology (telehealth, texting, video) is used to deliver service, that has its own written procedures.</t>
+          <t>Written job descriptions; verification of credentials before hire (including the state peer credential); background checks; documented orientation; competency-based training with documented competency, not just attendance; regular documented supervision; annual performance appraisal; and a documented look at workforce needs and succession.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>1J-01 Technology and System Planning</t>
+          <t>Annual Performance Appraisal</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Supervisor and employee</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3034,34 +3034,34 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>1.I</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>A written technology and systems plan covering the systems in use, who may access what, how data is backed up and tested, what happens when the system is down, and how confidentiality is protected. If information and communication technology (telehealth, texting, video) is used to deliver service, that has its own written procedures.</t>
+          <t>Written job descriptions; verification of credentials before hire (including the state peer credential); background checks; documented orientation; competency-based training with documented competency, not just attendance; regular documented supervision; annual performance appraisal; and a documented look at workforce needs and succession.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1J-02 Information Security and Confidentiality of Data</t>
+          <t>Credential and Background Verification Log</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Privacy Officer]</t>
+          <t>Chief Executive Officer or designee</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3076,27 +3076,27 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>1.I</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>A written technology and systems plan covering the systems in use, who may access what, how data is backed up and tested, what happens when the system is down, and how confidentiality is protected. If information and communication technology (telehealth, texting, video) is used to deliver service, that has its own written procedures.</t>
+          <t>Written job descriptions; verification of credentials before hire (including the state peer credential); background checks; documented orientation; competency-based training with documented competency, not just attendance; regular documented supervision; annual performance appraisal; and a documented look at workforce needs and succession.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>1J-03 Social Media, Mobile Devices, and Electronic Communication</t>
+          <t>Individual Training Log</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
@@ -3118,34 +3118,34 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>1.I</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>A written technology and systems plan covering the systems in use, who may access what, how data is backed up and tested, what happens when the system is down, and how confidentiality is protected. If information and communication technology (telehealth, texting, video) is used to deliver service, that has its own written procedures.</t>
+          <t>Written job descriptions; verification of credentials before hire (including the state peer credential); background checks; documented orientation; competency-based training with documented competency, not just attendance; regular documented supervision; annual performance appraisal; and a documented look at workforce needs and succession.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1J-04 Information and Communication Technology in Service Delivery (Telehealth)</t>
+          <t>Personnel File Checklist</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>Chief Executive Officer or designee</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -3175,12 +3175,12 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Technology and System Plan</t>
+          <t>1J-01 Technology and System Planning</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Written plan</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
@@ -3217,19 +3217,19 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>System Downtime Service Log and Procedure</t>
+          <t>1J-02 Information Security and Confidentiality of Data</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>All staff</t>
+          <t>[FILL IN: Privacy Officer]</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3259,19 +3259,19 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Device and System Access Log</t>
+          <t>1J-03 Social Media, Mobile Devices, and Electronic Communication</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Privacy Officer]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3286,22 +3286,22 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Rights of Persons Served</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Rights are written, given to and explained to every person served in a way they can understand, and posted. There is a written grievance/complaint process with timeframes and an appeal, a grievance log, informed consent, and confidentiality protections. Rights are reviewed annually for whether they were actually honored.</t>
+          <t>A written technology and systems plan covering the systems in use, who may access what, how data is backed up and tested, what happens when the system is down, and how confidentiality is protected. If information and communication technology (telehealth, texting, video) is used to deliver service, that has its own written procedures.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1K-01 Rights of the Persons Served</t>
+          <t>1J-04 Information and Communication Technology in Service Delivery (Telehealth)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3328,34 +3328,34 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Rights of Persons Served</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Rights are written, given to and explained to every person served in a way they can understand, and posted. There is a written grievance/complaint process with timeframes and an appeal, a grievance log, informed consent, and confidentiality protections. Rights are reviewed annually for whether they were actually honored.</t>
+          <t>A written technology and systems plan covering the systems in use, who may access what, how data is backed up and tested, what happens when the system is down, and how confidentiality is protected. If information and communication technology (telehealth, texting, video) is used to deliver service, that has its own written procedures.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>1K-02 Grievances, Complaints, and Appeals</t>
+          <t>Technology and System Plan</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Written plan</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3370,34 +3370,34 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Rights of Persons Served</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Rights are written, given to and explained to every person served in a way they can understand, and posted. There is a written grievance/complaint process with timeframes and an appeal, a grievance log, informed consent, and confidentiality protections. Rights are reviewed annually for whether they were actually honored.</t>
+          <t>A written technology and systems plan covering the systems in use, who may access what, how data is backed up and tested, what happens when the system is down, and how confidentiality is protected. If information and communication technology (telehealth, texting, video) is used to deliver service, that has its own written procedures.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1K-03 Confidentiality and Release of Information</t>
+          <t>System Downtime Service Log and Procedure</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Privacy Officer]</t>
+          <t>All staff</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -3412,34 +3412,34 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Rights of Persons Served</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Rights are written, given to and explained to every person served in a way they can understand, and posted. There is a written grievance/complaint process with timeframes and an appeal, a grievance log, informed consent, and confidentiality protections. Rights are reviewed annually for whether they were actually honored.</t>
+          <t>A written technology and systems plan covering the systems in use, who may access what, how data is backed up and tested, what happens when the system is down, and how confidentiality is protected. If information and communication technology (telehealth, texting, video) is used to deliver service, that has its own written procedures.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>1K-04 Informed Consent for Services</t>
+          <t>Device and System Access Log</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Privacy Officer]</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3469,19 +3469,19 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Your Rights — Handout for Persons Served</t>
+          <t>1K-01 Rights of the Persons Served</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Every person served</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -3511,19 +3511,19 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Complaint / Grievance Form</t>
+          <t>1K-02 Grievances, Complaints, and Appeals</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Person served, family, guardian, or any stakeholder</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -3553,19 +3553,19 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Grievance and Complaint Log</t>
+          <t>1K-03 Confidentiality and Release of Information</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Privacy Officer]</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -3595,19 +3595,19 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Consent for Services</t>
+          <t>1K-04 Informed Consent for Services</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Person served or legal representative</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Authorization to Release Information</t>
+          <t>Your Rights — Handout for Persons Served</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Person served or legal representative</t>
+          <t>Every person served</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Acknowledgment of Receipt — Notice of Privacy Practices</t>
+          <t>Complaint / Grievance Form</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Person served</t>
+          <t>Person served, family, guardian, or any stakeholder</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Annual Review — Were Rights Actually Honored?</t>
+          <t>Grievance and Complaint Log</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3733,7 +3733,7 @@
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name] and [FILL IN: Quality Improvement Coordinator]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -3748,34 +3748,34 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>1.L</t>
+          <t>1.K</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Rights of Persons Served</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>A written accessibility plan that identifies real barriers in eight areas - architectural, environmental, attitudinal, financial, employment, communication, transportation, and digital/technology - names an action and a responsible person for each, and is reviewed annually with progress documented.</t>
+          <t>Rights are written, given to and explained to every person served in a way they can understand, and posted. There is a written grievance/complaint process with timeframes and an appeal, a grievance log, informed consent, and confidentiality protections. Rights are reviewed annually for whether they were actually honored.</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>1L-01 Accessibility</t>
+          <t>Consent for Services</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Person served or legal representative</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
@@ -3790,34 +3790,34 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>1.L</t>
+          <t>1.K</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Rights of Persons Served</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>A written accessibility plan that identifies real barriers in eight areas - architectural, environmental, attitudinal, financial, employment, communication, transportation, and digital/technology - names an action and a responsible person for each, and is reviewed annually with progress documented.</t>
+          <t>Rights are written, given to and explained to every person served in a way they can understand, and posted. There is a written grievance/complaint process with timeframes and an appeal, a grievance log, informed consent, and confidentiality protections. Rights are reviewed annually for whether they were actually honored.</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Accessibility Plan</t>
+          <t>Authorization to Release Information</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Written plan</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Person served or legal representative</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
@@ -3832,22 +3832,22 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>1.L</t>
+          <t>1.K</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Rights of Persons Served</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>A written accessibility plan that identifies real barriers in eight areas - architectural, environmental, attitudinal, financial, employment, communication, transportation, and digital/technology - names an action and a responsible person for each, and is reviewed annually with progress documented.</t>
+          <t>Rights are written, given to and explained to every person served in a way they can understand, and posted. There is a written grievance/complaint process with timeframes and an appeal, a grievance log, informed consent, and confidentiality protections. Rights are reviewed annually for whether they were actually honored.</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Accessibility Barrier Survey</t>
+          <t>Acknowledgment of Receipt — Notice of Privacy Practices</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer with input from persons served and personnel</t>
+          <t>Person served</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -3874,34 +3874,34 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>1.K</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Performance Measurement and Management</t>
+          <t>Rights of Persons Served</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>The organization decides in writing what it will measure, why, how, how often, and what the target is - covering both business function and service delivery, and covering effectiveness, efficiency, service access, and satisfaction. Data is actually collected and reported on schedule.</t>
+          <t>Rights are written, given to and explained to every person served in a way they can understand, and posted. There is a written grievance/complaint process with timeframes and an appeal, a grievance log, informed consent, and confidentiality protections. Rights are reviewed annually for whether they were actually honored.</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>1M-01 Performance Measurement and Management</t>
+          <t>Annual Review — Were Rights Actually Honored?</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>[FILL IN: Program Director name] and [FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -3916,27 +3916,27 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Performance Measurement and Management</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>The organization decides in writing what it will measure, why, how, how often, and what the target is - covering both business function and service delivery, and covering effectiveness, efficiency, service access, and satisfaction. Data is actually collected and reported on schedule.</t>
+          <t>A written accessibility plan that identifies real barriers in eight areas - architectural, environmental, attitudinal, financial, employment, communication, transportation, and digital/technology - names an action and a responsible person for each, and is reviewed annually with progress documented.</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Performance Measurement and Management Plan</t>
+          <t>1L-01 Accessibility</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Written plan</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
@@ -3958,34 +3958,34 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Performance Measurement and Management</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>The organization decides in writing what it will measure, why, how, how often, and what the target is - covering both business function and service delivery, and covering effectiveness, efficiency, service access, and satisfaction. Data is actually collected and reported on schedule.</t>
+          <t>A written accessibility plan that identifies real barriers in eight areas - architectural, environmental, attitudinal, financial, employment, communication, transportation, and digital/technology - names an action and a responsible person for each, and is reviewed annually with progress documented.</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Measure Definition Sheet</t>
+          <t>Accessibility Plan</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Written plan</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
@@ -4000,22 +4000,22 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Performance Measurement and Management</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>The organization decides in writing what it will measure, why, how, how often, and what the target is - covering both business function and service delivery, and covering effectiveness, efficiency, service access, and satisfaction. Data is actually collected and reported on schedule.</t>
+          <t>A written accessibility plan that identifies real barriers in eight areas - architectural, environmental, attitudinal, financial, employment, communication, transportation, and digital/technology - names an action and a responsible person for each, and is reviewed annually with progress documented.</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Quarterly Performance Dashboard</t>
+          <t>Accessibility Barrier Survey</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4027,7 +4027,7 @@
       <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>Chief Executive Officer with input from persons served and personnel</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr"/>
@@ -4042,22 +4042,22 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Performance Improvement</t>
+          <t>Performance Measurement and Management</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>The measured data is analyzed at least annually in a written performance analysis, conclusions are drawn, improvement actions are taken and tracked, and the results are shared with staff, persons served, and other stakeholders in a format they can understand.</t>
+          <t>The organization decides in writing what it will measure, why, how, how often, and what the target is - covering both business function and service delivery, and covering effectiveness, efficiency, service access, and satisfaction. Data is actually collected and reported on schedule.</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>1N-01 Performance Improvement</t>
+          <t>1M-01 Performance Measurement and Management</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4084,22 +4084,22 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Performance Improvement</t>
+          <t>Performance Measurement and Management</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>The measured data is analyzed at least annually in a written performance analysis, conclusions are drawn, improvement actions are taken and tracked, and the results are shared with staff, persons served, and other stakeholders in a format they can understand.</t>
+          <t>The organization decides in writing what it will measure, why, how, how often, and what the target is - covering both business function and service delivery, and covering effectiveness, efficiency, service access, and satisfaction. Data is actually collected and reported on schedule.</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Performance Improvement Plan and Annual Analysis Template</t>
+          <t>Performance Measurement and Management Plan</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4126,22 +4126,22 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Performance Improvement</t>
+          <t>Performance Measurement and Management</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>The measured data is analyzed at least annually in a written performance analysis, conclusions are drawn, improvement actions are taken and tracked, and the results are shared with staff, persons served, and other stakeholders in a format they can understand.</t>
+          <t>The organization decides in writing what it will measure, why, how, how often, and what the target is - covering both business function and service delivery, and covering effectiveness, efficiency, service access, and satisfaction. Data is actually collected and reported on schedule.</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Annual Performance Analysis Report — Cover and Sign-Off</t>
+          <t>Measure Definition Sheet</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4168,22 +4168,22 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Performance Improvement</t>
+          <t>Performance Measurement and Management</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>The measured data is analyzed at least annually in a written performance analysis, conclusions are drawn, improvement actions are taken and tracked, and the results are shared with staff, persons served, and other stakeholders in a format they can understand.</t>
+          <t>The organization decides in writing what it will measure, why, how, how often, and what the target is - covering both business function and service delivery, and covering effectiveness, efficiency, service access, and satisfaction. Data is actually collected and reported on schedule.</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Performance Improvement Project Charter</t>
+          <t>Quarterly Performance Dashboard</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Project owner</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
@@ -4225,12 +4225,12 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>"You Said, We Did" — Results Summary for Persons Served and Stakeholders</t>
+          <t>1N-01 Performance Improvement</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
@@ -4252,34 +4252,34 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>1.N</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Program/Service Structure</t>
+          <t>Performance Improvement</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>A written program description that says who the program serves, what it does, where and when, who delivers it and with what qualifications, and how it connects people to community resources. Services are person-centered and recovery-oriented, and staffing is sufficient for the people served.</t>
+          <t>The measured data is analyzed at least annually in a written performance analysis, conclusions are drawn, improvement actions are taken and tracked, and the results are shared with staff, persons served, and other stakeholders in a format they can understand.</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>2A-01 Program Description and Service Structure</t>
+          <t>Performance Improvement Plan and Annual Analysis Template</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Written plan</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
@@ -4294,34 +4294,34 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>1.N</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Program/Service Structure</t>
+          <t>Performance Improvement</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>A written program description that says who the program serves, what it does, where and when, who delivers it and with what qualifications, and how it connects people to community resources. Services are person-centered and recovery-oriented, and staffing is sufficient for the people served.</t>
+          <t>The measured data is analyzed at least annually in a written performance analysis, conclusions are drawn, improvement actions are taken and tracked, and the results are shared with staff, persons served, and other stakeholders in a format they can understand.</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>2A-02 Community Resources and Coordination of Care</t>
+          <t>Annual Performance Analysis Report — Cover and Sign-Off</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
@@ -4336,22 +4336,22 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>1.N</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Program/Service Structure</t>
+          <t>Performance Improvement</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>A written program description that says who the program serves, what it does, where and when, who delivers it and with what qualifications, and how it connects people to community resources. Services are person-centered and recovery-oriented, and staffing is sufficient for the people served.</t>
+          <t>The measured data is analyzed at least annually in a written performance analysis, conclusions are drawn, improvement actions are taken and tracked, and the results are shared with staff, persons served, and other stakeholders in a format they can understand.</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Program Description</t>
+          <t>Performance Improvement Project Charter</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -4363,7 +4363,7 @@
       <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>Project owner</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
@@ -4378,22 +4378,22 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>1.N</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Program/Service Structure</t>
+          <t>Performance Improvement</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>A written program description that says who the program serves, what it does, where and when, who delivers it and with what qualifications, and how it connects people to community resources. Services are person-centered and recovery-oriented, and staffing is sufficient for the people served.</t>
+          <t>The measured data is analyzed at least annually in a written performance analysis, conclusions are drawn, improvement actions are taken and tracked, and the results are shared with staff, persons served, and other stakeholders in a format they can understand.</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Community Resource Directory</t>
+          <t>"You Said, We Did" — Results Summary for Persons Served and Stakeholders</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -4405,7 +4405,7 @@
       <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
@@ -4435,12 +4435,12 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Staffing Plan</t>
+          <t>2A-01 Program Description and Service Structure</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
@@ -4462,22 +4462,22 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Screening and Access to Services</t>
+          <t>Program/Service Structure</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Written eligibility criteria, a documented screening process with timeframes, what happens when someone is not eligible or must wait, and a documented orientation for every person entering the program that covers rights, grievance, confidentiality, fees, and what to expect.</t>
+          <t>A written program description that says who the program serves, what it does, where and when, who delivers it and with what qualifications, and how it connects people to community resources. Services are person-centered and recovery-oriented, and staffing is sufficient for the people served.</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>2B-01 Screening, Eligibility, and Access to Services</t>
+          <t>2A-02 Community Resources and Coordination of Care</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -4504,27 +4504,27 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Screening and Access to Services</t>
+          <t>Program/Service Structure</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Written eligibility criteria, a documented screening process with timeframes, what happens when someone is not eligible or must wait, and a documented orientation for every person entering the program that covers rights, grievance, confidentiality, fees, and what to expect.</t>
+          <t>A written program description that says who the program serves, what it does, where and when, who delivers it and with what qualifications, and how it connects people to community resources. Services are person-centered and recovery-oriented, and staffing is sufficient for the people served.</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>2B-02 Orientation of the Person Served</t>
+          <t>Program Description</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
@@ -4546,22 +4546,22 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Screening and Access to Services</t>
+          <t>Program/Service Structure</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Written eligibility criteria, a documented screening process with timeframes, what happens when someone is not eligible or must wait, and a documented orientation for every person entering the program that covers rights, grievance, confidentiality, fees, and what to expect.</t>
+          <t>A written program description that says who the program serves, what it does, where and when, who delivers it and with what qualifications, and how it connects people to community resources. Services are person-centered and recovery-oriented, and staffing is sufficient for the people served.</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Screening and Referral Form</t>
+          <t>Community Resource Directory</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Staff receiving the referral</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
@@ -4588,22 +4588,22 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Screening and Access to Services</t>
+          <t>Program/Service Structure</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Written eligibility criteria, a documented screening process with timeframes, what happens when someone is not eligible or must wait, and a documented orientation for every person entering the program that covers rights, grievance, confidentiality, fees, and what to expect.</t>
+          <t>A written program description that says who the program serves, what it does, where and when, who delivers it and with what qualifications, and how it connects people to community resources. Services are person-centered and recovery-oriented, and staffing is sufficient for the people served.</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Waiting List Log</t>
+          <t>Staffing Plan</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -4645,19 +4645,19 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Orientation of the Person Served</t>
+          <t>2B-01 Screening, Eligibility, and Access to Services</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Peer Support Specialist with the person served</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
@@ -4687,12 +4687,12 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Referral-Out Log (People We Could Not Serve)</t>
+          <t>2B-02 Orientation of the Person Served</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr"/>
@@ -4714,34 +4714,34 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Person-Centered Plan</t>
+          <t>Screening and Access to Services</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Each person has an individualized plan built with them, in their own words, reflecting their strengths, needs, abilities and preferences, with goals and measurable objectives, the specific services and who provides them, target dates, and the person's signature. The plan is reviewed on a stated schedule and updated when things change.</t>
+          <t>Written eligibility criteria, a documented screening process with timeframes, what happens when someone is not eligible or must wait, and a documented orientation for every person entering the program that covers rights, grievance, confidentiality, fees, and what to expect.</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>2C-01 Person-Centered Planning</t>
+          <t>Screening and Referral Form</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>Staff receiving the referral</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
@@ -4756,34 +4756,34 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Person-Centered Plan</t>
+          <t>Screening and Access to Services</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Each person has an individualized plan built with them, in their own words, reflecting their strengths, needs, abilities and preferences, with goals and measurable objectives, the specific services and who provides them, target dates, and the person's signature. The plan is reviewed on a stated schedule and updated when things change.</t>
+          <t>Written eligibility criteria, a documented screening process with timeframes, what happens when someone is not eligible or must wait, and a documented orientation for every person entering the program that covers rights, grievance, confidentiality, fees, and what to expect.</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>2C-02 Plan Review and Documentation of Services</t>
+          <t>Waiting List Log</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Supervisor of the peer workforce]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
@@ -4798,22 +4798,22 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Person-Centered Plan</t>
+          <t>Screening and Access to Services</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Each person has an individualized plan built with them, in their own words, reflecting their strengths, needs, abilities and preferences, with goals and measurable objectives, the specific services and who provides them, target dates, and the person's signature. The plan is reviewed on a stated schedule and updated when things change.</t>
+          <t>Written eligibility criteria, a documented screening process with timeframes, what happens when someone is not eligible or must wait, and a documented orientation for every person entering the program that covers rights, grievance, confidentiality, fees, and what to expect.</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Person-Centered Plan</t>
+          <t>Orientation of the Person Served</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>The person served, with their Peer Support Specialist</t>
+          <t>Peer Support Specialist with the person served</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
@@ -4840,22 +4840,22 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Person-Centered Plan</t>
+          <t>Screening and Access to Services</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Each person has an individualized plan built with them, in their own words, reflecting their strengths, needs, abilities and preferences, with goals and measurable objectives, the specific services and who provides them, target dates, and the person's signature. The plan is reviewed on a stated schedule and updated when things change.</t>
+          <t>Written eligibility criteria, a documented screening process with timeframes, what happens when someone is not eligible or must wait, and a documented orientation for every person entering the program that covers rights, grievance, confidentiality, fees, and what to expect.</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Person-Centered Plan Review</t>
+          <t>Referral-Out Log (People We Could Not Serve)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>The person served, with their Peer Support Specialist</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr"/>
@@ -4897,19 +4897,19 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>My Wellness and Recovery Plan</t>
+          <t>2C-01 Person-Centered Planning</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>The person served, supported by their Peer Support Specialist</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr"/>
@@ -4939,19 +4939,19 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Peer Support Progress Note</t>
+          <t>2C-02 Plan Review and Documentation of Services</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>The staff member who delivered the service</t>
+          <t>[FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
@@ -4966,34 +4966,34 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Transition/Discharge</t>
+          <t>Person-Centered Plan</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Transition planning begins at admission, not at the end. There is a written transition/discharge summary for every person who leaves, including unplanned exits, and a documented attempt at follow-up after discharge with the results recorded and analyzed.</t>
+          <t>Each person has an individualized plan built with them, in their own words, reflecting their strengths, needs, abilities and preferences, with goals and measurable objectives, the specific services and who provides them, target dates, and the person's signature. The plan is reviewed on a stated schedule and updated when things change.</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>2D-01 Transition Planning</t>
+          <t>Person-Centered Plan</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>The person served, with their Peer Support Specialist</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
@@ -5008,34 +5008,34 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Transition/Discharge</t>
+          <t>Person-Centered Plan</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Transition planning begins at admission, not at the end. There is a written transition/discharge summary for every person who leaves, including unplanned exits, and a documented attempt at follow-up after discharge with the results recorded and analyzed.</t>
+          <t>Each person has an individualized plan built with them, in their own words, reflecting their strengths, needs, abilities and preferences, with goals and measurable objectives, the specific services and who provides them, target dates, and the person's signature. The plan is reviewed on a stated schedule and updated when things change.</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>2D-02 Discharge Summary and Follow-Up</t>
+          <t>Person-Centered Plan Review</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>The person served, with their Peer Support Specialist</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
@@ -5050,22 +5050,22 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Transition/Discharge</t>
+          <t>Person-Centered Plan</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Transition planning begins at admission, not at the end. There is a written transition/discharge summary for every person who leaves, including unplanned exits, and a documented attempt at follow-up after discharge with the results recorded and analyzed.</t>
+          <t>Each person has an individualized plan built with them, in their own words, reflecting their strengths, needs, abilities and preferences, with goals and measurable objectives, the specific services and who provides them, target dates, and the person's signature. The plan is reviewed on a stated schedule and updated when things change.</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Transition / Discharge Summary</t>
+          <t>My Wellness and Recovery Plan</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -5077,7 +5077,7 @@
       <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Peer Support Specialist and Supervisor</t>
+          <t>The person served, supported by their Peer Support Specialist</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
@@ -5092,22 +5092,22 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Transition/Discharge</t>
+          <t>Person-Centered Plan</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Transition planning begins at admission, not at the end. There is a written transition/discharge summary for every person who leaves, including unplanned exits, and a documented attempt at follow-up after discharge with the results recorded and analyzed.</t>
+          <t>Each person has an individualized plan built with them, in their own words, reflecting their strengths, needs, abilities and preferences, with goals and measurable objectives, the specific services and who provides them, target dates, and the person's signature. The plan is reviewed on a stated schedule and updated when things change.</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Post-Discharge Follow-Up Contact Log</t>
+          <t>Peer Support Progress Note</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
       <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>The staff member who delivered the service</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>
@@ -5149,19 +5149,19 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Unplanned Exit Review</t>
+          <t>2D-01 Transition Planning</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name] with the Peer Support Specialist</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
@@ -5176,22 +5176,22 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>2.E</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Medication Use</t>
+          <t>Transition/Discharge</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>If the program does not prescribe, dispense, administer, or store medication, that must be stated in writing, and staff must know their limits and what to do about medication questions and adverse reactions. If it does any of those things, a full medication management policy set is required.</t>
+          <t>Transition planning begins at admission, not at the end. There is a written transition/discharge summary for every person who leaves, including unplanned exits, and a documented attempt at follow-up after discharge with the results recorded and analyzed.</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>2E-01 Medication</t>
+          <t>2D-02 Discharge Summary and Follow-Up</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -5218,22 +5218,22 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>2.E</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Medication Use</t>
+          <t>Transition/Discharge</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>If the program does not prescribe, dispense, administer, or store medication, that must be stated in writing, and staff must know their limits and what to do about medication questions and adverse reactions. If it does any of those things, a full medication management policy set is required.</t>
+          <t>Transition planning begins at admission, not at the end. There is a written transition/discharge summary for every person who leaves, including unplanned exits, and a documented attempt at follow-up after discharge with the results recorded and analyzed.</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Medication — What Your Peer Specialist Can and Cannot Do</t>
+          <t>Transition / Discharge Summary</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Person served</t>
+          <t>Peer Support Specialist and Supervisor</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
@@ -5260,27 +5260,27 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Nonviolent Practices</t>
+          <t>Transition/Discharge</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>A written commitment to nonviolent practice: de-escalation training for staff, what is prohibited, what to do in a behavioral crisis, when to call for help, and a debriefing with the person served and staff after any crisis event.</t>
+          <t>Transition planning begins at admission, not at the end. There is a written transition/discharge summary for every person who leaves, including unplanned exits, and a documented attempt at follow-up after discharge with the results recorded and analyzed.</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>2F-01 Nonviolent Practices</t>
+          <t>Post-Discharge Follow-Up Contact Log</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr"/>
@@ -5302,34 +5302,34 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Nonviolent Practices</t>
+          <t>Transition/Discharge</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>A written commitment to nonviolent practice: de-escalation training for staff, what is prohibited, what to do in a behavioral crisis, when to call for help, and a debriefing with the person served and staff after any crisis event.</t>
+          <t>Transition planning begins at admission, not at the end. There is a written transition/discharge summary for every person who leaves, including unplanned exits, and a documented attempt at follow-up after discharge with the results recorded and analyzed.</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>2F-02 Crisis Response and Debriefing</t>
+          <t>Unplanned Exit Review</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Supervisor of the peer workforce]</t>
+          <t>[FILL IN: Program Director name] with the Peer Support Specialist</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
@@ -5344,34 +5344,34 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.E</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Nonviolent Practices</t>
+          <t>Medication Use</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>A written commitment to nonviolent practice: de-escalation training for staff, what is prohibited, what to do in a behavioral crisis, when to call for help, and a debriefing with the person served and staff after any crisis event.</t>
+          <t>If the program does not prescribe, dispense, administer, or store medication, that must be stated in writing, and staff must know their limits and what to do about medication questions and adverse reactions. If it does any of those things, a full medication management policy set is required.</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Crisis Debriefing Form</t>
+          <t>2E-01 Medication</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Supervisor of the peer workforce]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr"/>
@@ -5386,22 +5386,22 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.E</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Nonviolent Practices</t>
+          <t>Medication Use</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>A written commitment to nonviolent practice: de-escalation training for staff, what is prohibited, what to do in a behavioral crisis, when to call for help, and a debriefing with the person served and staff after any crisis event.</t>
+          <t>If the program does not prescribe, dispense, administer, or store medication, that must be stated in writing, and staff must know their limits and what to do about medication questions and adverse reactions. If it does any of those things, a full medication management policy set is required.</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>De-escalation and Nonviolent Practices Training Log</t>
+          <t>Medication — What Your Peer Specialist Can and Cannot Do</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>Person served</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
@@ -5443,19 +5443,19 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>My Personal Safety and Crisis Plan</t>
+          <t>2F-01 Nonviolent Practices</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>The person served, with their Peer Support Specialist</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr"/>
@@ -5470,22 +5470,22 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>2.G</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Records of the Persons Served</t>
+          <t>Nonviolent Practices</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>A written list of what belongs in a record, who may write in it, how quickly entries must be made, how corrections are made, how records are secured, how long they are kept, and how they are destroyed. Entries are legible, dated, and signed with credential.</t>
+          <t>A written commitment to nonviolent practice: de-escalation training for staff, what is prohibited, what to do in a behavioral crisis, when to call for help, and a debriefing with the person served and staff after any crisis event.</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>2G-01 Content and Maintenance of the Record of the Person Served</t>
+          <t>2F-02 Crisis Response and Debriefing</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -5497,7 +5497,7 @@
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr"/>
@@ -5512,34 +5512,34 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>2.G</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Records of the Persons Served</t>
+          <t>Nonviolent Practices</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>A written list of what belongs in a record, who may write in it, how quickly entries must be made, how corrections are made, how records are secured, how long they are kept, and how they are destroyed. Entries are legible, dated, and signed with credential.</t>
+          <t>A written commitment to nonviolent practice: de-escalation training for staff, what is prohibited, what to do in a behavioral crisis, when to call for help, and a debriefing with the person served and staff after any crisis event.</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>2G-02 Records Retention, Access, and Destruction</t>
+          <t>Crisis Debriefing Form</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Privacy Officer]</t>
+          <t>[FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr"/>
@@ -5554,22 +5554,22 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>2.G</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Records of the Persons Served</t>
+          <t>Nonviolent Practices</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>A written list of what belongs in a record, who may write in it, how quickly entries must be made, how corrections are made, how records are secured, how long they are kept, and how they are destroyed. Entries are legible, dated, and signed with credential.</t>
+          <t>A written commitment to nonviolent practice: de-escalation training for staff, what is prohibited, what to do in a behavioral crisis, when to call for help, and a debriefing with the person served and staff after any crisis event.</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Record Content Checklist</t>
+          <t>De-escalation and Nonviolent Practices Training Log</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -5581,7 +5581,7 @@
       <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator] or Supervisor</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr"/>
@@ -5596,22 +5596,22 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>2.G</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Records of the Persons Served</t>
+          <t>Nonviolent Practices</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>A written list of what belongs in a record, who may write in it, how quickly entries must be made, how corrections are made, how records are secured, how long they are kept, and how they are destroyed. Entries are legible, dated, and signed with credential.</t>
+          <t>A written commitment to nonviolent practice: de-escalation training for staff, what is prohibited, what to do in a behavioral crisis, when to call for help, and a debriefing with the person served and staff after any crisis event.</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Records Retention Schedule</t>
+          <t>My Personal Safety and Crisis Plan</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Privacy Officer]</t>
+          <t>The person served, with their Peer Support Specialist</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr"/>
@@ -5638,22 +5638,22 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>2.H</t>
+          <t>2.G</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Quality Record Review</t>
+          <t>Records of the Persons Served</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Records are reviewed on a written schedule using a written tool, by someone qualified, looking at whether documentation supports the service and the plan. Results are aggregated, trends identified, and corrective action tracked to closure.</t>
+          <t>A written list of what belongs in a record, who may write in it, how quickly entries must be made, how corrections are made, how records are secured, how long they are kept, and how they are destroyed. Entries are legible, dated, and signed with credential.</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>2H-01 Quality Record Review</t>
+          <t>2G-01 Content and Maintenance of the Record of the Person Served</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -5665,7 +5665,7 @@
       <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr"/>
@@ -5680,34 +5680,34 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>2.H</t>
+          <t>2.G</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Quality Record Review</t>
+          <t>Records of the Persons Served</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Records are reviewed on a written schedule using a written tool, by someone qualified, looking at whether documentation supports the service and the plan. Results are aggregated, trends identified, and corrective action tracked to closure.</t>
+          <t>A written list of what belongs in a record, who may write in it, how quickly entries must be made, how corrections are made, how records are secured, how long they are kept, and how they are destroyed. Entries are legible, dated, and signed with credential.</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Quality Record Review Tool</t>
+          <t>2G-02 Records Retention, Access, and Destruction</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator] or qualified designee who did not write the documentation</t>
+          <t>[FILL IN: Privacy Officer]</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr"/>
@@ -5722,22 +5722,22 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>2.H</t>
+          <t>2.G</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Quality Record Review</t>
+          <t>Records of the Persons Served</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Records are reviewed on a written schedule using a written tool, by someone qualified, looking at whether documentation supports the service and the plan. Results are aggregated, trends identified, and corrective action tracked to closure.</t>
+          <t>A written list of what belongs in a record, who may write in it, how quickly entries must be made, how corrections are made, how records are secured, how long they are kept, and how they are destroyed. Entries are legible, dated, and signed with credential.</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Quarterly Record Review Summary Report</t>
+          <t>Record Content Checklist</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
       <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>[FILL IN: Quality Improvement Coordinator] or Supervisor</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr"/>
@@ -5764,22 +5764,22 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>2.H</t>
+          <t>2.G</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Quality Record Review</t>
+          <t>Records of the Persons Served</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Records are reviewed on a written schedule using a written tool, by someone qualified, looking at whether documentation supports the service and the plan. Results are aggregated, trends identified, and corrective action tracked to closure.</t>
+          <t>A written list of what belongs in a record, who may write in it, how quickly entries must be made, how corrections are made, how records are secured, how long they are kept, and how they are destroyed. Entries are legible, dated, and signed with credential.</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Corrective Action Tracker</t>
+          <t>Records Retention Schedule</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>[FILL IN: Privacy Officer]</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr"/>
@@ -5806,22 +5806,22 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>2.H</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Community Integration</t>
+          <t>Quality Record Review</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>The program helps people participate in community life as they choose - housing, work, education, benefits, relationships, transportation, recreation, health care, and civic life. It is built on the person's own goals, uses natural supports and real community settings rather than segregated ones, and measures actual community participation, not just service contacts.</t>
+          <t>Records are reviewed on a written schedule using a written tool, by someone qualified, looking at whether documentation supports the service and the plan. Results are aggregated, trends identified, and corrective action tracked to closure.</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>3CI-01 Community Integration Program Philosophy and Scope</t>
+          <t>2H-01 Quality Record Review</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -5833,7 +5833,7 @@
       <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr"/>
@@ -5848,34 +5848,34 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>2.H</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Community Integration</t>
+          <t>Quality Record Review</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>The program helps people participate in community life as they choose - housing, work, education, benefits, relationships, transportation, recreation, health care, and civic life. It is built on the person's own goals, uses natural supports and real community settings rather than segregated ones, and measures actual community participation, not just service contacts.</t>
+          <t>Records are reviewed on a written schedule using a written tool, by someone qualified, looking at whether documentation supports the service and the plan. Results are aggregated, trends identified, and corrective action tracked to closure.</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>3CI-02 Choice, Self-Determination, and Dignity of Risk</t>
+          <t>Quality Record Review Tool</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Quality Improvement Coordinator] or qualified designee who did not write the documentation</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr"/>
@@ -5890,34 +5890,34 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>2.H</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Community Integration</t>
+          <t>Quality Record Review</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>The program helps people participate in community life as they choose - housing, work, education, benefits, relationships, transportation, recreation, health care, and civic life. It is built on the person's own goals, uses natural supports and real community settings rather than segregated ones, and measures actual community participation, not just service contacts.</t>
+          <t>Records are reviewed on a written schedule using a written tool, by someone qualified, looking at whether documentation supports the service and the plan. Results are aggregated, trends identified, and corrective action tracked to closure.</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>3CI-03 Natural Supports and Community Connection</t>
+          <t>Quarterly Record Review Summary Report</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr"/>
@@ -5932,34 +5932,34 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>2.H</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Community Integration</t>
+          <t>Quality Record Review</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>The program helps people participate in community life as they choose - housing, work, education, benefits, relationships, transportation, recreation, health care, and civic life. It is built on the person's own goals, uses natural supports and real community settings rather than segregated ones, and measures actual community participation, not just service contacts.</t>
+          <t>Records are reviewed on a written schedule using a written tool, by someone qualified, looking at whether documentation supports the service and the plan. Results are aggregated, trends identified, and corrective action tracked to closure.</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>3CI-04 Transportation and Community Outings</t>
+          <t>Corrective Action Tracker</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr"/>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>3CI-05 Advocacy, Benefits, and Removing Barriers</t>
+          <t>3CI-01 Community Integration Program Philosophy and Scope</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -6031,19 +6031,19 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Community Integration Goal Worksheet</t>
+          <t>3CI-02 Choice, Self-Determination, and Dignity of Risk</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>The person served with their Peer Support Specialist</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr"/>
@@ -6073,19 +6073,19 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Natural Supports Map</t>
+          <t>3CI-03 Natural Supports and Community Connection</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>The person served with their Peer Support Specialist</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr"/>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Community Resource Directory</t>
+          <t>3CI-04 Transportation and Community Outings</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr"/>
@@ -6157,19 +6157,19 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Benefits and Entitlements Checklist</t>
+          <t>3CI-05 Advocacy, Benefits, and Removing Barriers</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>The person served with their Peer Support Specialist</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr"/>
@@ -6184,34 +6184,34 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>3.CI</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Peer Workforce Requirements (cross-cutting)</t>
+          <t>Community Integration</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder.</t>
+          <t>The program helps people participate in community life as they choose - housing, work, education, benefits, relationships, transportation, recreation, health care, and civic life. It is built on the person's own goals, uses natural supports and real community settings rather than segregated ones, and measures actual community participation, not just service contacts.</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>3P-01 The Peer Support Service Model</t>
+          <t>Community Integration Goal Worksheet</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>The person served with their Peer Support Specialist</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr"/>
@@ -6226,34 +6226,34 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>3.CI</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Peer Workforce Requirements (cross-cutting)</t>
+          <t>Community Integration</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder.</t>
+          <t>The program helps people participate in community life as they choose - housing, work, education, benefits, relationships, transportation, recreation, health care, and civic life. It is built on the person's own goals, uses natural supports and real community settings rather than segregated ones, and measures actual community participation, not just service contacts.</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>3P-02 Self-Disclosure</t>
+          <t>Natural Supports Map</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Supervisor of the peer workforce]</t>
+          <t>The person served with their Peer Support Specialist</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr"/>
@@ -6268,34 +6268,34 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>3.CI</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Peer Workforce Requirements (cross-cutting)</t>
+          <t>Community Integration</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder.</t>
+          <t>The program helps people participate in community life as they choose - housing, work, education, benefits, relationships, transportation, recreation, health care, and civic life. It is built on the person's own goals, uses natural supports and real community settings rather than segregated ones, and measures actual community participation, not just service contacts.</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>3P-03 Boundaries and Dual Relationships</t>
+          <t>Community Resource Directory</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Supervisor of the peer workforce]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr"/>
@@ -6310,34 +6310,34 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>3.CI</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Peer Workforce Requirements (cross-cutting)</t>
+          <t>Community Integration</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder.</t>
+          <t>The program helps people participate in community life as they choose - housing, work, education, benefits, relationships, transportation, recreation, health care, and civic life. It is built on the person's own goals, uses natural supports and real community settings rather than segregated ones, and measures actual community participation, not just service contacts.</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>3P-04 Peer Workforce Wellness</t>
+          <t>Benefits and Entitlements Checklist</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>The person served with their Peer Support Specialist</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr"/>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>3P-05 Peer Specialist Credential, Scope, and Career Ladder</t>
+          <t>3P-01 The Peer Support Service Model</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -6379,7 +6379,7 @@
       <c r="G141" s="2" t="inlineStr"/>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr"/>
@@ -6409,19 +6409,19 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Job Description — Peer Support Specialist</t>
+          <t>3P-02 Self-Disclosure</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>Employee and supervisor sign at hire and at revision</t>
+          <t>[FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr"/>
@@ -6451,12 +6451,12 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Competency Assessment — Peer Support Specialist</t>
+          <t>3P-03 Boundaries and Dual Relationships</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
@@ -6493,19 +6493,19 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Self-Disclosure Supervision Worksheet</t>
+          <t>3P-04 Peer Workforce Wellness</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Peer Support Specialist with [FILL IN: Supervisor of the peer workforce]</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr"/>
@@ -6535,19 +6535,19 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Dual Relationship Disclosure and Management Plan</t>
+          <t>3P-05 Peer Specialist Credential, Scope, and Career Ladder</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Any staff member; management plan by [FILL IN: Supervisor of the peer workforce]</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr"/>
@@ -6577,7 +6577,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>My Peer Wellness Plan (Staff)</t>
+          <t>Job Description — Peer Support Specialist</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -6589,7 +6589,7 @@
       <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Peer Support Specialist with [FILL IN: Supervisor of the peer workforce]</t>
+          <t>Employee and supervisor sign at hire and at revision</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr"/>
@@ -6601,8 +6601,176 @@
         </is>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>3.PEER</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Peer Workforce Requirements (cross-cutting)</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder.</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Competency Assessment — Peer Support Specialist</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Form / evidence</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>[FILL IN: Supervisor of the peer workforce]</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>3.PEER</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Peer Workforce Requirements (cross-cutting)</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder.</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Self-Disclosure Supervision Worksheet</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Form / evidence</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>Peer Support Specialist with [FILL IN: Supervisor of the peer workforce]</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>3.PEER</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Peer Workforce Requirements (cross-cutting)</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder.</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Dual Relationship Disclosure and Management Plan</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Form / evidence</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>Any staff member; management plan by [FILL IN: Supervisor of the peer workforce]</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>3.PEER</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Peer Workforce Requirements (cross-cutting)</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder.</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>My Peer Wellness Plan (Staff)</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Form / evidence</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>Peer Support Specialist with [FILL IN: Supervisor of the peer workforce]</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L146"/>
+  <autoFilter ref="A1:L150"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6613,7 +6781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6729,17 +6897,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1.B</t>
+          <t>1.A</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Governing body, CEO</t>
+          <t>CEO, Governing body, Program Director</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>May I see twelve months of board minutes?</t>
+          <t>Show me one policy traced end to end: approved, published, staff trained, competency observed, and then checked in real practice.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
@@ -6748,17 +6916,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1.B</t>
+          <t>1.A</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Governing body, CEO</t>
+          <t>CEO, Governing body, Program Director</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>When did the board last evaluate the CEO?</t>
+          <t>How do you know staff are working from the current version and not last year's?</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
@@ -6777,7 +6945,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>How does the board assess its own performance?</t>
+          <t>May I see twelve months of board minutes?</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
@@ -6786,17 +6954,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1.C</t>
+          <t>1.B</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CEO, Governing body</t>
+          <t>Governing body, CEO</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Show me the strategic plan and the minutes where it was reviewed.</t>
+          <t>When did the board last evaluate the CEO?</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
@@ -6805,17 +6973,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1.C</t>
+          <t>1.B</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CEO, Governing body</t>
+          <t>Governing body, CEO</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>What data went into it?</t>
+          <t>How does the board assess its own performance?</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
@@ -6834,7 +7002,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>What changed as a result?</t>
+          <t>Show me the strategic plan and the minutes where it was reviewed.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
@@ -6843,17 +7011,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1.D</t>
+          <t>1.C</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Persons served, Program Director, QI Coordinator</t>
+          <t>CEO, Governing body</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Show me last year's satisfaction results.</t>
+          <t>What data went into it?</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
@@ -6862,17 +7030,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1.D</t>
+          <t>1.C</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Persons served, Program Director, QI Coordinator</t>
+          <t>CEO, Governing body</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>What did you change because of them?</t>
+          <t>What changed as a result?</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
@@ -6891,7 +7059,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>How did you tell the people served what changed?</t>
+          <t>Show me last year's satisfaction results.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
@@ -6900,17 +7068,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1.E</t>
+          <t>1.D</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CEO, Compliance Officer</t>
+          <t>Persons served, Program Director, QI Coordinator</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>What licenses and contracts are you operating under?</t>
+          <t>What did you change because of them?</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr"/>
@@ -6919,17 +7087,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1.E</t>
+          <t>1.D</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CEO, Compliance Officer</t>
+          <t>Persons served, Program Director, QI Coordinator</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Who tracks renewal dates?</t>
+          <t>How did you tell the people served what changed?</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
@@ -6948,7 +7116,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Show me the current license certificate.</t>
+          <t>What licenses and contracts are you operating under?</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
@@ -6957,17 +7125,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1.F</t>
+          <t>1.E</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CEO, Finance</t>
+          <t>CEO, Compliance Officer</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Show me the budget and the monthly comparison to actual.</t>
+          <t>Who tracks renewal dates?</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
@@ -6976,17 +7144,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1.F</t>
+          <t>1.E</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CEO, Finance</t>
+          <t>CEO, Compliance Officer</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Who signs checks and who reconciles the bank statement?</t>
+          <t>Show me the current license certificate.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
@@ -7005,7 +7173,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Show me the most recent external review or audit.</t>
+          <t>Show me the budget and the monthly comparison to actual.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
@@ -7014,17 +7182,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1.G</t>
+          <t>1.F</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CEO, Program Director</t>
+          <t>CEO, Finance</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>What are your top risks and what are you doing about them?</t>
+          <t>Who signs checks and who reconciles the bank statement?</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
@@ -7033,17 +7201,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1.G</t>
+          <t>1.F</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CEO, Program Director</t>
+          <t>CEO, Finance</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Show me your insurance declarations page.</t>
+          <t>Show me the most recent external review or audit.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
@@ -7062,7 +7230,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>When was the plan last reviewed and by whom?</t>
+          <t>What are your top risks and what are you doing about them?</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
@@ -7071,17 +7239,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>1.H</t>
+          <t>1.G</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Safety Officer, Direct staff, Persons served</t>
+          <t>CEO, Program Director</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Show me a year of drill records for every shift and every emergency type.</t>
+          <t>Show me your insurance declarations page.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
@@ -7090,17 +7258,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1.H</t>
+          <t>1.G</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Safety Officer, Direct staff, Persons served</t>
+          <t>CEO, Program Director</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Walk me through what happens if a peer specialist feels unsafe at a home visit.</t>
+          <t>When was the plan last reviewed and by whom?</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
@@ -7119,7 +7287,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Show me your incident log and the analysis of trends.</t>
+          <t>Show me a year of drill records for every shift and every emergency type.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
@@ -7128,17 +7296,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1.I</t>
+          <t>1.H</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>HR, Supervisor, Peer Support Specialists</t>
+          <t>Safety Officer, Direct staff, Persons served</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Pull three personnel files. Show me credential verification, orientation, competency, supervision, and the last appraisal in each.</t>
+          <t>Walk me through what happens if a peer specialist feels unsafe at a home visit.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
@@ -7147,17 +7315,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1.I</t>
+          <t>1.H</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>HR, Supervisor, Peer Support Specialists</t>
+          <t>Safety Officer, Direct staff, Persons served</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>How do you know a new peer specialist is competent, not just trained?</t>
+          <t>Show me your incident log and the analysis of trends.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
@@ -7176,7 +7344,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Show me the supervision notes for the last six months.</t>
+          <t>Pull three personnel files. Show me credential verification, orientation, competency, supervision, and the last appraisal in each.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
@@ -7185,17 +7353,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>1.I</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CEO, Privacy Officer, Direct staff</t>
+          <t>HR, Supervisor, Peer Support Specialists</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>What happens to service delivery if your EHR is down for two days?</t>
+          <t>How do you know a new peer specialist is competent, not just trained?</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
@@ -7204,17 +7372,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>1.J</t>
+          <t>1.I</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CEO, Privacy Officer, Direct staff</t>
+          <t>HR, Supervisor, Peer Support Specialists</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>When did you last test a restore from backup?</t>
+          <t>Show me the supervision notes for the last six months.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
@@ -7233,7 +7401,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Show me your texting and social media rules for peer staff.</t>
+          <t>What happens to service delivery if your EHR is down for two days?</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
@@ -7242,17 +7410,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Persons served, Direct staff, Privacy Officer</t>
+          <t>CEO, Privacy Officer, Direct staff</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Ask a person served: do you know how to file a complaint?</t>
+          <t>When did you last test a restore from backup?</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
@@ -7261,17 +7429,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Persons served, Direct staff, Privacy Officer</t>
+          <t>CEO, Privacy Officer, Direct staff</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Show me the grievance log and what happened with each one.</t>
+          <t>Show me your texting and social media rules for peer staff.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
@@ -7290,7 +7458,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Show me signed consents in three records.</t>
+          <t>Ask a person served: do you know how to file a complaint?</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
@@ -7299,17 +7467,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1.L</t>
+          <t>1.K</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CEO, Persons served, Direct staff</t>
+          <t>Persons served, Direct staff, Privacy Officer</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Show me your accessibility plan and this year's progress.</t>
+          <t>Show me the grievance log and what happened with each one.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
@@ -7318,17 +7486,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>1.L</t>
+          <t>1.K</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CEO, Persons served, Direct staff</t>
+          <t>Persons served, Direct staff, Privacy Officer</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>What barrier did you remove in the last twelve months?</t>
+          <t>Show me signed consents in three records.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
@@ -7347,7 +7515,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>How would a person who is deaf access your service?</t>
+          <t>Show me your accessibility plan and this year's progress.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
@@ -7356,17 +7524,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>QI Coordinator, CEO, Program Director</t>
+          <t>CEO, Persons served, Direct staff</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>What exactly do you measure and what is your target?</t>
+          <t>What barrier did you remove in the last twelve months?</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
@@ -7375,17 +7543,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>QI Coordinator, CEO, Program Director</t>
+          <t>CEO, Persons served, Direct staff</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Show me the data for the last four quarters.</t>
+          <t>How would a person who is deaf access your service?</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
@@ -7404,7 +7572,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>How do you define a successful outcome for a person in peer support?</t>
+          <t>What exactly do you measure and what is your target?</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
@@ -7413,17 +7581,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>QI Coordinator, CEO, Direct staff, Persons served</t>
+          <t>QI Coordinator, CEO, Program Director</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Show me last year's written performance analysis.</t>
+          <t>Show me the data for the last four quarters.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -7432,17 +7600,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>QI Coordinator, CEO, Direct staff, Persons served</t>
+          <t>QI Coordinator, CEO, Program Director</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Name one improvement project and show me the before and after numbers.</t>
+          <t>How do you define a successful outcome for a person in peer support?</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -7461,7 +7629,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>How did the people you serve find out about these results?</t>
+          <t>Show me last year's written performance analysis.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -7470,17 +7638,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>1.N</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Program Director, Direct staff</t>
+          <t>QI Coordinator, CEO, Direct staff, Persons served</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Show me the written program description.</t>
+          <t>Name one improvement project and show me the before and after numbers.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -7489,17 +7657,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>1.N</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Program Director, Direct staff</t>
+          <t>QI Coordinator, CEO, Direct staff, Persons served</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Does what I am seeing on site match what this says?</t>
+          <t>How did the people you serve find out about these results?</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -7518,7 +7686,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>How many people can one peer specialist carry, and how did you decide that?</t>
+          <t>Show me the written program description.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -7527,17 +7695,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Program Director, Direct staff, Persons served</t>
+          <t>Program Director, Direct staff</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>How long between the referral and the first contact? Prove it.</t>
+          <t>Does what I am seeing on site match what this says?</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -7546,17 +7714,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Program Director, Direct staff, Persons served</t>
+          <t>Program Director, Direct staff</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Show me a signed orientation checklist in a record.</t>
+          <t>How many people can one peer specialist carry, and how did you decide that?</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -7575,7 +7743,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>What do you do when someone does not meet criteria?</t>
+          <t>How long between the referral and the first contact? Prove it.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -7584,17 +7752,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Persons served, Direct staff, Supervisor</t>
+          <t>Program Director, Direct staff, Persons served</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Read me a goal in the person's own words.</t>
+          <t>Show me a signed orientation checklist in a record.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -7603,17 +7771,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Persons served, Direct staff, Supervisor</t>
+          <t>Program Director, Direct staff, Persons served</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Show me where the person signed and dated the plan.</t>
+          <t>What do you do when someone does not meet criteria?</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -7632,7 +7800,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Show me the review that was due last month.</t>
+          <t>Read me a goal in the person's own words.</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -7651,7 +7819,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Does this progress note connect to a goal on this plan?</t>
+          <t>Show me where the person signed and dated the plan.</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
@@ -7660,17 +7828,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Program Director, Direct staff</t>
+          <t>Persons served, Direct staff, Supervisor</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Show me discharge summaries for the last five people who left, including the ones who just stopped coming.</t>
+          <t>Show me the review that was due last month.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
@@ -7679,17 +7847,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Program Director, Direct staff</t>
+          <t>Persons served, Direct staff, Supervisor</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>What does your follow-up data tell you?</t>
+          <t>Does this progress note connect to a goal on this plan?</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -7698,7 +7866,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2.E</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -7708,7 +7876,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Do you touch medication in any way?</t>
+          <t>Show me discharge summaries for the last five people who left, including the ones who just stopped coming.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
@@ -7717,7 +7885,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2.E</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -7727,7 +7895,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Ask a peer specialist: what do you do if someone tells you they stopped their medication?</t>
+          <t>What does your follow-up data tell you?</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
@@ -7736,17 +7904,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.E</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Direct staff, Supervisor, Persons served</t>
+          <t>Program Director, Direct staff</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>What restraint or seclusion do you use? (correct answer for most peer programs: none, and it is prohibited in writing)</t>
+          <t>Do you touch medication in any way?</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
@@ -7755,17 +7923,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.E</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Direct staff, Supervisor, Persons served</t>
+          <t>Program Director, Direct staff</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Ask staff: what do you do if someone escalates in the car?</t>
+          <t>Ask a peer specialist: what do you do if someone tells you they stopped their medication?</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
@@ -7784,7 +7952,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Show me a debriefing after your last crisis event.</t>
+          <t>What restraint or seclusion do you use? (correct answer for most peer programs: none, and it is prohibited in writing)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
@@ -7793,17 +7961,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2.G</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Program Director, Direct staff, Records custodian</t>
+          <t>Direct staff, Supervisor, Persons served</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>What is your documentation timeframe and can you prove notes meet it?</t>
+          <t>Ask staff: what do you do if someone escalates in the car?</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
@@ -7812,17 +7980,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>2.G</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Program Director, Direct staff, Records custodian</t>
+          <t>Direct staff, Supervisor, Persons served</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Where are paper records kept and who has the key?</t>
+          <t>Show me a debriefing after your last crisis event.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
@@ -7841,7 +8009,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Show me how a correction is made.</t>
+          <t>What is your documentation timeframe and can you prove notes meet it?</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
@@ -7850,17 +8018,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>2.H</t>
+          <t>2.G</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>QI Coordinator, Supervisor</t>
+          <t>Program Director, Direct staff, Records custodian</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Show me your last four quarterly record reviews.</t>
+          <t>Where are paper records kept and who has the key?</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
@@ -7869,17 +8037,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2.H</t>
+          <t>2.G</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>QI Coordinator, Supervisor</t>
+          <t>Program Director, Direct staff, Records custodian</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>What did you find and what did you do about it?</t>
+          <t>Show me how a correction is made.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -7898,7 +8066,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Show me that the correction actually happened.</t>
+          <t>Show me your last four quarterly record reviews.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -7907,17 +8075,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>2.H</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Persons served, Direct staff, Program Director</t>
+          <t>QI Coordinator, Supervisor</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Show me a person who moved into their own housing, got a job, or joined something in the community because of you.</t>
+          <t>What did you find and what did you do about it?</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
@@ -7926,17 +8094,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>2.H</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Persons served, Direct staff, Program Director</t>
+          <t>QI Coordinator, Supervisor</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>How do you measure community participation?</t>
+          <t>Show me that the correction actually happened.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
@@ -7955,7 +8123,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Ask a person served: what do you want that we are helping you get?</t>
+          <t>Show me a person who moved into their own housing, got a job, or joined something in the community because of you.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
@@ -7964,17 +8132,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>3.CI</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Peer Support Specialists, Supervisor, Program Director</t>
+          <t>Persons served, Direct staff, Program Director</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>What makes someone qualified to be a peer specialist here?</t>
+          <t>How do you measure community participation?</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
@@ -7983,17 +8151,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>3.CI</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Peer Support Specialists, Supervisor, Program Director</t>
+          <t>Persons served, Direct staff, Program Director</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>How do you supervise self-disclosure?</t>
+          <t>Ask a person served: what do you want that we are helping you get?</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
@@ -8012,7 +8180,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>What happens when a peer specialist knows a participant from their own recovery community?</t>
+          <t>What makes someone qualified to be a peer specialist here?</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
@@ -8031,11 +8199,49 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>How do you protect the wellness of staff in recovery?</t>
+          <t>How do you supervise self-disclosure?</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>3.PEER</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Peer Support Specialists, Supervisor, Program Director</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>What happens when a peer specialist knows a participant from their own recovery community?</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>3.PEER</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Peer Support Specialists, Supervisor, Program Director</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>How do you protect the wellness of staff in recovery?</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/.claude/skills/carf-peer-support-accreditation/providers/example-peer-agency/output/05_Self_Study_Checklist.xlsx
+++ b/.claude/skills/carf-peer-support-accreditation/providers/example-peer-agency/output/05_Self_Study_Checklist.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interview Prep" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Self-Study'!$A$1:$L$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Self-Study'!$A$1:$L$151</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L150"/>
+  <dimension ref="A1:L151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Governance (Optional)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Governance (Optional)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Governance (Optional)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Governance (Optional)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Strategic Integrated Planning</t>
+          <t>Strategic Planning</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Strategic Integrated Planning</t>
+          <t>Strategic Planning</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Strategic Integrated Planning</t>
+          <t>Strategic Planning</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Workforce Development and Management</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Workforce Development and Management</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Workforce Development and Management</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Workforce Development and Management</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Workforce Development and Management</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Workforce Development and Management</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Workforce Development and Management</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Workforce Development and Management</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Workforce Development and Management</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Workforce Development and Management</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Workforce Development and Management</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Workforce Development and Management</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Workforce Development and Management</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Workforce Development and Management</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Workforce Development and Management</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Workforce Development and Management</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3165,17 +3165,17 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Rights of Persons Served</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>A written technology and systems plan covering the systems in use, who may access what, how data is backed up and tested, what happens when the system is down, and how confidentiality is protected. If information and communication technology (telehealth, texting, video) is used to deliver service, that has its own written procedures.</t>
+          <t>Rights are written, given to and explained to every person served in a way they can understand, and posted. There is a written grievance/complaint process with timeframes and an appeal, a grievance log, informed consent, and confidentiality protections. Rights are reviewed annually for whether they were actually honored.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>1J-01 Technology and System Planning</t>
+          <t>1J-01 Rights of the Persons Served</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -3207,17 +3207,17 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Rights of Persons Served</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>A written technology and systems plan covering the systems in use, who may access what, how data is backed up and tested, what happens when the system is down, and how confidentiality is protected. If information and communication technology (telehealth, texting, video) is used to deliver service, that has its own written procedures.</t>
+          <t>Rights are written, given to and explained to every person served in a way they can understand, and posted. There is a written grievance/complaint process with timeframes and an appeal, a grievance log, informed consent, and confidentiality protections. Rights are reviewed annually for whether they were actually honored.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1J-02 Information Security and Confidentiality of Data</t>
+          <t>1J-02 Grievances, Complaints, and Appeals</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3229,7 +3229,7 @@
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Privacy Officer]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3249,17 +3249,17 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Rights of Persons Served</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>A written technology and systems plan covering the systems in use, who may access what, how data is backed up and tested, what happens when the system is down, and how confidentiality is protected. If information and communication technology (telehealth, texting, video) is used to deliver service, that has its own written procedures.</t>
+          <t>Rights are written, given to and explained to every person served in a way they can understand, and posted. There is a written grievance/complaint process with timeframes and an appeal, a grievance log, informed consent, and confidentiality protections. Rights are reviewed annually for whether they were actually honored.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>1J-03 Social Media, Mobile Devices, and Electronic Communication</t>
+          <t>1J-03 Confidentiality and Release of Information</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Privacy Officer]</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3291,17 +3291,17 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Rights of Persons Served</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>A written technology and systems plan covering the systems in use, who may access what, how data is backed up and tested, what happens when the system is down, and how confidentiality is protected. If information and communication technology (telehealth, texting, video) is used to deliver service, that has its own written procedures.</t>
+          <t>Rights are written, given to and explained to every person served in a way they can understand, and posted. There is a written grievance/complaint process with timeframes and an appeal, a grievance log, informed consent, and confidentiality protections. Rights are reviewed annually for whether they were actually honored.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1J-04 Information and Communication Technology in Service Delivery (Telehealth)</t>
+          <t>1J-04 Informed Consent for Services</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3333,29 +3333,29 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Rights of Persons Served</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>A written technology and systems plan covering the systems in use, who may access what, how data is backed up and tested, what happens when the system is down, and how confidentiality is protected. If information and communication technology (telehealth, texting, video) is used to deliver service, that has its own written procedures.</t>
+          <t>Rights are written, given to and explained to every person served in a way they can understand, and posted. There is a written grievance/complaint process with timeframes and an appeal, a grievance log, informed consent, and confidentiality protections. Rights are reviewed annually for whether they were actually honored.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Technology and System Plan</t>
+          <t>Your Rights — Handout for Persons Served</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Written plan</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Every person served</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3375,17 +3375,17 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Rights of Persons Served</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>A written technology and systems plan covering the systems in use, who may access what, how data is backed up and tested, what happens when the system is down, and how confidentiality is protected. If information and communication technology (telehealth, texting, video) is used to deliver service, that has its own written procedures.</t>
+          <t>Rights are written, given to and explained to every person served in a way they can understand, and posted. There is a written grievance/complaint process with timeframes and an appeal, a grievance log, informed consent, and confidentiality protections. Rights are reviewed annually for whether they were actually honored.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>System Downtime Service Log and Procedure</t>
+          <t>Complaint / Grievance Form</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>All staff</t>
+          <t>Person served, family, guardian, or any stakeholder</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -3417,17 +3417,17 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Rights of Persons Served</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>A written technology and systems plan covering the systems in use, who may access what, how data is backed up and tested, what happens when the system is down, and how confidentiality is protected. If information and communication technology (telehealth, texting, video) is used to deliver service, that has its own written procedures.</t>
+          <t>Rights are written, given to and explained to every person served in a way they can understand, and posted. There is a written grievance/complaint process with timeframes and an appeal, a grievance log, informed consent, and confidentiality protections. Rights are reviewed annually for whether they were actually honored.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Device and System Access Log</t>
+          <t>Grievance and Complaint Log</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3439,7 +3439,7 @@
       <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Privacy Officer]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3454,7 +3454,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1K-01 Rights of the Persons Served</t>
+          <t>Consent for Services</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>Person served or legal representative</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -3496,7 +3496,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3511,19 +3511,19 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>1K-02 Grievances, Complaints, and Appeals</t>
+          <t>Authorization to Release Information</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>Person served or legal representative</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -3538,7 +3538,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3553,19 +3553,19 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>1K-03 Confidentiality and Release of Information</t>
+          <t>Acknowledgment of Receipt — Notice of Privacy Practices</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Privacy Officer]</t>
+          <t>Person served</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -3580,7 +3580,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.J</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3595,19 +3595,19 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>1K-04 Informed Consent for Services</t>
+          <t>Annual Review — Were Rights Actually Honored?</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Program Director name] and [FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -3627,29 +3627,29 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Rights of Persons Served</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Rights are written, given to and explained to every person served in a way they can understand, and posted. There is a written grievance/complaint process with timeframes and an appeal, a grievance log, informed consent, and confidentiality protections. Rights are reviewed annually for whether they were actually honored.</t>
+          <t>A written accessibility plan that identifies real barriers in eight areas - architectural, environmental, attitudinal, financial, employment, communication, transportation, and digital/technology - names an action and a responsible person for each, and is reviewed annually with progress documented.</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Your Rights — Handout for Persons Served</t>
+          <t>1K-01 Accessibility</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Every person served</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -3669,29 +3669,29 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Rights of Persons Served</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Rights are written, given to and explained to every person served in a way they can understand, and posted. There is a written grievance/complaint process with timeframes and an appeal, a grievance log, informed consent, and confidentiality protections. Rights are reviewed annually for whether they were actually honored.</t>
+          <t>A written accessibility plan that identifies real barriers in eight areas - architectural, environmental, attitudinal, financial, employment, communication, transportation, and digital/technology - names an action and a responsible person for each, and is reviewed annually with progress documented.</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Complaint / Grievance Form</t>
+          <t>Accessibility Plan</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Written plan</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Person served, family, guardian, or any stakeholder</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -3711,17 +3711,17 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Rights of Persons Served</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Rights are written, given to and explained to every person served in a way they can understand, and posted. There is a written grievance/complaint process with timeframes and an appeal, a grievance log, informed consent, and confidentiality protections. Rights are reviewed annually for whether they were actually honored.</t>
+          <t>A written accessibility plan that identifies real barriers in eight areas - architectural, environmental, attitudinal, financial, employment, communication, transportation, and digital/technology - names an action and a responsible person for each, and is reviewed annually with progress documented.</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Grievance and Complaint Log</t>
+          <t>Accessibility Barrier Survey</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3733,7 +3733,7 @@
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>Chief Executive Officer with input from persons served and personnel</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -3748,34 +3748,34 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Rights of Persons Served</t>
+          <t>Performance Measurement and Management</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Rights are written, given to and explained to every person served in a way they can understand, and posted. There is a written grievance/complaint process with timeframes and an appeal, a grievance log, informed consent, and confidentiality protections. Rights are reviewed annually for whether they were actually honored.</t>
+          <t>The organization decides in writing what it will measure, why, how, how often, and what the target is - covering both business function and service delivery, and covering effectiveness, efficiency, service access, and satisfaction. Data is actually collected and reported on schedule.</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Consent for Services</t>
+          <t>1L-01 Performance Measurement and Management</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Person served or legal representative</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
@@ -3790,34 +3790,34 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Rights of Persons Served</t>
+          <t>Performance Measurement and Management</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Rights are written, given to and explained to every person served in a way they can understand, and posted. There is a written grievance/complaint process with timeframes and an appeal, a grievance log, informed consent, and confidentiality protections. Rights are reviewed annually for whether they were actually honored.</t>
+          <t>The organization decides in writing what it will measure, why, how, how often, and what the target is - covering both business function and service delivery, and covering effectiveness, efficiency, service access, and satisfaction. Data is actually collected and reported on schedule.</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Authorization to Release Information</t>
+          <t>Performance Measurement and Management Plan</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Written plan</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Person served or legal representative</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
@@ -3832,22 +3832,22 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Rights of Persons Served</t>
+          <t>Performance Measurement and Management</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Rights are written, given to and explained to every person served in a way they can understand, and posted. There is a written grievance/complaint process with timeframes and an appeal, a grievance log, informed consent, and confidentiality protections. Rights are reviewed annually for whether they were actually honored.</t>
+          <t>The organization decides in writing what it will measure, why, how, how often, and what the target is - covering both business function and service delivery, and covering effectiveness, efficiency, service access, and satisfaction. Data is actually collected and reported on schedule.</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Acknowledgment of Receipt — Notice of Privacy Practices</t>
+          <t>Measure Definition Sheet</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Person served</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -3874,22 +3874,22 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>1.K</t>
+          <t>1.L</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Rights of Persons Served</t>
+          <t>Performance Measurement and Management</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Rights are written, given to and explained to every person served in a way they can understand, and posted. There is a written grievance/complaint process with timeframes and an appeal, a grievance log, informed consent, and confidentiality protections. Rights are reviewed annually for whether they were actually honored.</t>
+          <t>The organization decides in writing what it will measure, why, how, how often, and what the target is - covering both business function and service delivery, and covering effectiveness, efficiency, service access, and satisfaction. Data is actually collected and reported on schedule.</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Annual Review — Were Rights Actually Honored?</t>
+          <t>Quarterly Performance Dashboard</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -3901,7 +3901,7 @@
       <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name] and [FILL IN: Quality Improvement Coordinator]</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -3916,22 +3916,22 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>1.L</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Performance Improvement</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>A written accessibility plan that identifies real barriers in eight areas - architectural, environmental, attitudinal, financial, employment, communication, transportation, and digital/technology - names an action and a responsible person for each, and is reviewed annually with progress documented.</t>
+          <t>The measured data is analyzed at least annually in a written performance analysis, conclusions are drawn, improvement actions are taken and tracked, and the results are shared with staff, persons served, and other stakeholders in a format they can understand.</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>1L-01 Accessibility</t>
+          <t>1M-01 Performance Improvement</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -3943,7 +3943,7 @@
       <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
@@ -3958,22 +3958,22 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>1.L</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Performance Improvement</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>A written accessibility plan that identifies real barriers in eight areas - architectural, environmental, attitudinal, financial, employment, communication, transportation, and digital/technology - names an action and a responsible person for each, and is reviewed annually with progress documented.</t>
+          <t>The measured data is analyzed at least annually in a written performance analysis, conclusions are drawn, improvement actions are taken and tracked, and the results are shared with staff, persons served, and other stakeholders in a format they can understand.</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Accessibility Plan</t>
+          <t>Performance Improvement Plan and Annual Analysis Template</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4000,22 +4000,22 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>1.L</t>
+          <t>1.M</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Performance Improvement</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>A written accessibility plan that identifies real barriers in eight areas - architectural, environmental, attitudinal, financial, employment, communication, transportation, and digital/technology - names an action and a responsible person for each, and is reviewed annually with progress documented.</t>
+          <t>The measured data is analyzed at least annually in a written performance analysis, conclusions are drawn, improvement actions are taken and tracked, and the results are shared with staff, persons served, and other stakeholders in a format they can understand.</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Accessibility Barrier Survey</t>
+          <t>Annual Performance Analysis Report — Cover and Sign-Off</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4027,7 +4027,7 @@
       <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer with input from persons served and personnel</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr"/>
@@ -4047,29 +4047,29 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Performance Measurement and Management</t>
+          <t>Performance Improvement</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>The organization decides in writing what it will measure, why, how, how often, and what the target is - covering both business function and service delivery, and covering effectiveness, efficiency, service access, and satisfaction. Data is actually collected and reported on schedule.</t>
+          <t>The measured data is analyzed at least annually in a written performance analysis, conclusions are drawn, improvement actions are taken and tracked, and the results are shared with staff, persons served, and other stakeholders in a format they can understand.</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>1M-01 Performance Measurement and Management</t>
+          <t>Performance Improvement Project Charter</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>Project owner</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
@@ -4089,29 +4089,29 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Performance Measurement and Management</t>
+          <t>Performance Improvement</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>The organization decides in writing what it will measure, why, how, how often, and what the target is - covering both business function and service delivery, and covering effectiveness, efficiency, service access, and satisfaction. Data is actually collected and reported on schedule.</t>
+          <t>The measured data is analyzed at least annually in a written performance analysis, conclusions are drawn, improvement actions are taken and tracked, and the results are shared with staff, persons served, and other stakeholders in a format they can understand.</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Performance Measurement and Management Plan</t>
+          <t>"You Said, We Did" — Results Summary for Persons Served and Stakeholders</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Written plan</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
@@ -4126,34 +4126,34 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Performance Measurement and Management</t>
+          <t>Program/Service Structure</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>The organization decides in writing what it will measure, why, how, how often, and what the target is - covering both business function and service delivery, and covering effectiveness, efficiency, service access, and satisfaction. Data is actually collected and reported on schedule.</t>
+          <t>A written program description that says who the program serves, what it does, where and when, who delivers it and with what qualifications, and how it connects people to community resources. Services are person-centered and recovery-oriented, and staffing is sufficient for the people served.</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Measure Definition Sheet</t>
+          <t>2A-01 Program Description and Service Structure</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
@@ -4168,34 +4168,34 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>1.M</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Performance Measurement and Management</t>
+          <t>Program/Service Structure</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>The organization decides in writing what it will measure, why, how, how often, and what the target is - covering both business function and service delivery, and covering effectiveness, efficiency, service access, and satisfaction. Data is actually collected and reported on schedule.</t>
+          <t>A written program description that says who the program serves, what it does, where and when, who delivers it and with what qualifications, and how it connects people to community resources. Services are person-centered and recovery-oriented, and staffing is sufficient for the people served.</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Quarterly Performance Dashboard</t>
+          <t>2A-02 Community Resources and Coordination of Care</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
@@ -4210,34 +4210,34 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Performance Improvement</t>
+          <t>Program/Service Structure</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>The measured data is analyzed at least annually in a written performance analysis, conclusions are drawn, improvement actions are taken and tracked, and the results are shared with staff, persons served, and other stakeholders in a format they can understand.</t>
+          <t>A written program description that says who the program serves, what it does, where and when, who delivers it and with what qualifications, and how it connects people to community resources. Services are person-centered and recovery-oriented, and staffing is sufficient for the people served.</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>1N-01 Performance Improvement</t>
+          <t>Program Description</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
@@ -4252,34 +4252,34 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Performance Improvement</t>
+          <t>Program/Service Structure</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>The measured data is analyzed at least annually in a written performance analysis, conclusions are drawn, improvement actions are taken and tracked, and the results are shared with staff, persons served, and other stakeholders in a format they can understand.</t>
+          <t>A written program description that says who the program serves, what it does, where and when, who delivers it and with what qualifications, and how it connects people to community resources. Services are person-centered and recovery-oriented, and staffing is sufficient for the people served.</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Performance Improvement Plan and Annual Analysis Template</t>
+          <t>Community Resource Directory</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Written plan</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
@@ -4294,22 +4294,22 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Performance Improvement</t>
+          <t>Program/Service Structure</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>The measured data is analyzed at least annually in a written performance analysis, conclusions are drawn, improvement actions are taken and tracked, and the results are shared with staff, persons served, and other stakeholders in a format they can understand.</t>
+          <t>A written program description that says who the program serves, what it does, where and when, who delivers it and with what qualifications, and how it connects people to community resources. Services are person-centered and recovery-oriented, and staffing is sufficient for the people served.</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Annual Performance Analysis Report — Cover and Sign-Off</t>
+          <t>Staffing Plan</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
       <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
@@ -4336,34 +4336,34 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Performance Improvement</t>
+          <t>Screening and Access to Services</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>The measured data is analyzed at least annually in a written performance analysis, conclusions are drawn, improvement actions are taken and tracked, and the results are shared with staff, persons served, and other stakeholders in a format they can understand.</t>
+          <t>Written eligibility criteria, a documented screening process with timeframes, what happens when someone is not eligible or must wait, and a documented orientation for every person entering the program that covers rights, grievance, confidentiality, fees, and what to expect.</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Performance Improvement Project Charter</t>
+          <t>2B-01 Screening, Eligibility, and Access to Services</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Project owner</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
@@ -4378,34 +4378,34 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Performance Improvement</t>
+          <t>Screening and Access to Services</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>The measured data is analyzed at least annually in a written performance analysis, conclusions are drawn, improvement actions are taken and tracked, and the results are shared with staff, persons served, and other stakeholders in a format they can understand.</t>
+          <t>Written eligibility criteria, a documented screening process with timeframes, what happens when someone is not eligible or must wait, and a documented orientation for every person entering the program that covers rights, grievance, confidentiality, fees, and what to expect.</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>"You Said, We Did" — Results Summary for Persons Served and Stakeholders</t>
+          <t>2B-02 Orientation of the Person Served</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
@@ -4420,34 +4420,34 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Program/Service Structure</t>
+          <t>Screening and Access to Services</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>A written program description that says who the program serves, what it does, where and when, who delivers it and with what qualifications, and how it connects people to community resources. Services are person-centered and recovery-oriented, and staffing is sufficient for the people served.</t>
+          <t>Written eligibility criteria, a documented screening process with timeframes, what happens when someone is not eligible or must wait, and a documented orientation for every person entering the program that covers rights, grievance, confidentiality, fees, and what to expect.</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>2A-01 Program Description and Service Structure</t>
+          <t>Screening and Referral Form</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>Staff receiving the referral</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
@@ -4462,27 +4462,27 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Program/Service Structure</t>
+          <t>Screening and Access to Services</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>A written program description that says who the program serves, what it does, where and when, who delivers it and with what qualifications, and how it connects people to community resources. Services are person-centered and recovery-oriented, and staffing is sufficient for the people served.</t>
+          <t>Written eligibility criteria, a documented screening process with timeframes, what happens when someone is not eligible or must wait, and a documented orientation for every person entering the program that covers rights, grievance, confidentiality, fees, and what to expect.</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>2A-02 Community Resources and Coordination of Care</t>
+          <t>Waiting List Log</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
@@ -4504,22 +4504,22 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Program/Service Structure</t>
+          <t>Screening and Access to Services</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>A written program description that says who the program serves, what it does, where and when, who delivers it and with what qualifications, and how it connects people to community resources. Services are person-centered and recovery-oriented, and staffing is sufficient for the people served.</t>
+          <t>Written eligibility criteria, a documented screening process with timeframes, what happens when someone is not eligible or must wait, and a documented orientation for every person entering the program that covers rights, grievance, confidentiality, fees, and what to expect.</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Program Description</t>
+          <t>Orientation of the Person Served</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>Peer Support Specialist with the person served</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr"/>
@@ -4546,22 +4546,22 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Program/Service Structure</t>
+          <t>Screening and Access to Services</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>A written program description that says who the program serves, what it does, where and when, who delivers it and with what qualifications, and how it connects people to community resources. Services are person-centered and recovery-oriented, and staffing is sufficient for the people served.</t>
+          <t>Written eligibility criteria, a documented screening process with timeframes, what happens when someone is not eligible or must wait, and a documented orientation for every person entering the program that covers rights, grievance, confidentiality, fees, and what to expect.</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Community Resource Directory</t>
+          <t>Referral-Out Log (People We Could Not Serve)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -4588,27 +4588,27 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Program/Service Structure</t>
+          <t>Person-Centered Planning</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>A written program description that says who the program serves, what it does, where and when, who delivers it and with what qualifications, and how it connects people to community resources. Services are person-centered and recovery-oriented, and staffing is sufficient for the people served.</t>
+          <t>Each person has an individualized plan built with them, in their own words, reflecting their strengths, needs, abilities and preferences, with goals and measurable objectives, the specific services and who provides them, target dates, and the person's signature. The plan is reviewed on a stated schedule and updated when things change.</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Staffing Plan</t>
+          <t>2C-01 Person-Centered Planning</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr"/>
@@ -4630,22 +4630,22 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Screening and Access to Services</t>
+          <t>Person-Centered Planning</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Written eligibility criteria, a documented screening process with timeframes, what happens when someone is not eligible or must wait, and a documented orientation for every person entering the program that covers rights, grievance, confidentiality, fees, and what to expect.</t>
+          <t>Each person has an individualized plan built with them, in their own words, reflecting their strengths, needs, abilities and preferences, with goals and measurable objectives, the specific services and who provides them, target dates, and the person's signature. The plan is reviewed on a stated schedule and updated when things change.</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>2B-01 Screening, Eligibility, and Access to Services</t>
+          <t>2C-02 Plan Review and Documentation of Services</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -4657,7 +4657,7 @@
       <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
@@ -4672,34 +4672,34 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Screening and Access to Services</t>
+          <t>Person-Centered Planning</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Written eligibility criteria, a documented screening process with timeframes, what happens when someone is not eligible or must wait, and a documented orientation for every person entering the program that covers rights, grievance, confidentiality, fees, and what to expect.</t>
+          <t>Each person has an individualized plan built with them, in their own words, reflecting their strengths, needs, abilities and preferences, with goals and measurable objectives, the specific services and who provides them, target dates, and the person's signature. The plan is reviewed on a stated schedule and updated when things change.</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>2B-02 Orientation of the Person Served</t>
+          <t>Person-Centered Plan</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>The person served, with their Peer Support Specialist</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
@@ -4714,22 +4714,22 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Screening and Access to Services</t>
+          <t>Person-Centered Planning</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Written eligibility criteria, a documented screening process with timeframes, what happens when someone is not eligible or must wait, and a documented orientation for every person entering the program that covers rights, grievance, confidentiality, fees, and what to expect.</t>
+          <t>Each person has an individualized plan built with them, in their own words, reflecting their strengths, needs, abilities and preferences, with goals and measurable objectives, the specific services and who provides them, target dates, and the person's signature. The plan is reviewed on a stated schedule and updated when things change.</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Screening and Referral Form</t>
+          <t>Person-Centered Plan Review</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Staff receiving the referral</t>
+          <t>The person served, with their Peer Support Specialist</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
@@ -4756,22 +4756,22 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Screening and Access to Services</t>
+          <t>Person-Centered Planning</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Written eligibility criteria, a documented screening process with timeframes, what happens when someone is not eligible or must wait, and a documented orientation for every person entering the program that covers rights, grievance, confidentiality, fees, and what to expect.</t>
+          <t>Each person has an individualized plan built with them, in their own words, reflecting their strengths, needs, abilities and preferences, with goals and measurable objectives, the specific services and who provides them, target dates, and the person's signature. The plan is reviewed on a stated schedule and updated when things change.</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Waiting List Log</t>
+          <t>My Wellness and Recovery Plan</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>The person served, supported by their Peer Support Specialist</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
@@ -4798,22 +4798,22 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Screening and Access to Services</t>
+          <t>Person-Centered Planning</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Written eligibility criteria, a documented screening process with timeframes, what happens when someone is not eligible or must wait, and a documented orientation for every person entering the program that covers rights, grievance, confidentiality, fees, and what to expect.</t>
+          <t>Each person has an individualized plan built with them, in their own words, reflecting their strengths, needs, abilities and preferences, with goals and measurable objectives, the specific services and who provides them, target dates, and the person's signature. The plan is reviewed on a stated schedule and updated when things change.</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Orientation of the Person Served</t>
+          <t>Peer Support Progress Note</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Peer Support Specialist with the person served</t>
+          <t>The staff member who delivered the service</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
@@ -4840,27 +4840,27 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Screening and Access to Services</t>
+          <t>Transition/Discharge</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Written eligibility criteria, a documented screening process with timeframes, what happens when someone is not eligible or must wait, and a documented orientation for every person entering the program that covers rights, grievance, confidentiality, fees, and what to expect.</t>
+          <t>Transition planning begins at admission, not at the end. There is a written transition/discharge summary for every person who leaves, including unplanned exits, and a documented attempt at follow-up after discharge with the results recorded and analyzed.</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Referral-Out Log (People We Could Not Serve)</t>
+          <t>2D-01 Transition Planning</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr"/>
@@ -4882,22 +4882,22 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Person-Centered Plan</t>
+          <t>Transition/Discharge</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Each person has an individualized plan built with them, in their own words, reflecting their strengths, needs, abilities and preferences, with goals and measurable objectives, the specific services and who provides them, target dates, and the person's signature. The plan is reviewed on a stated schedule and updated when things change.</t>
+          <t>Transition planning begins at admission, not at the end. There is a written transition/discharge summary for every person who leaves, including unplanned exits, and a documented attempt at follow-up after discharge with the results recorded and analyzed.</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>2C-01 Person-Centered Planning</t>
+          <t>2D-02 Discharge Summary and Follow-Up</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -4924,34 +4924,34 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Person-Centered Plan</t>
+          <t>Transition/Discharge</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Each person has an individualized plan built with them, in their own words, reflecting their strengths, needs, abilities and preferences, with goals and measurable objectives, the specific services and who provides them, target dates, and the person's signature. The plan is reviewed on a stated schedule and updated when things change.</t>
+          <t>Transition planning begins at admission, not at the end. There is a written transition/discharge summary for every person who leaves, including unplanned exits, and a documented attempt at follow-up after discharge with the results recorded and analyzed.</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>2C-02 Plan Review and Documentation of Services</t>
+          <t>Transition / Discharge Summary</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Supervisor of the peer workforce]</t>
+          <t>Peer Support Specialist and Supervisor</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
@@ -4966,22 +4966,22 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Person-Centered Plan</t>
+          <t>Transition/Discharge</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Each person has an individualized plan built with them, in their own words, reflecting their strengths, needs, abilities and preferences, with goals and measurable objectives, the specific services and who provides them, target dates, and the person's signature. The plan is reviewed on a stated schedule and updated when things change.</t>
+          <t>Transition planning begins at admission, not at the end. There is a written transition/discharge summary for every person who leaves, including unplanned exits, and a documented attempt at follow-up after discharge with the results recorded and analyzed.</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Person-Centered Plan</t>
+          <t>Post-Discharge Follow-Up Contact Log</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -4993,7 +4993,7 @@
       <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>The person served, with their Peer Support Specialist</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
@@ -5008,22 +5008,22 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Person-Centered Plan</t>
+          <t>Transition/Discharge</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Each person has an individualized plan built with them, in their own words, reflecting their strengths, needs, abilities and preferences, with goals and measurable objectives, the specific services and who provides them, target dates, and the person's signature. The plan is reviewed on a stated schedule and updated when things change.</t>
+          <t>Transition planning begins at admission, not at the end. There is a written transition/discharge summary for every person who leaves, including unplanned exits, and a documented attempt at follow-up after discharge with the results recorded and analyzed.</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Person-Centered Plan Review</t>
+          <t>Unplanned Exit Review</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -5035,7 +5035,7 @@
       <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>The person served, with their Peer Support Specialist</t>
+          <t>[FILL IN: Program Director name] with the Peer Support Specialist</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
@@ -5050,34 +5050,34 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.E</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Person-Centered Plan</t>
+          <t>Medication Use</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Each person has an individualized plan built with them, in their own words, reflecting their strengths, needs, abilities and preferences, with goals and measurable objectives, the specific services and who provides them, target dates, and the person's signature. The plan is reviewed on a stated schedule and updated when things change.</t>
+          <t>If the program does not prescribe, dispense, administer, or store medication, that must be stated in writing, and staff must know their limits and what to do about medication questions and adverse reactions. If it does any of those things, a full medication management policy set is required.</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>My Wellness and Recovery Plan</t>
+          <t>2E-01 Medication</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>The person served, supported by their Peer Support Specialist</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
@@ -5092,22 +5092,22 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.E</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Person-Centered Plan</t>
+          <t>Medication Use</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Each person has an individualized plan built with them, in their own words, reflecting their strengths, needs, abilities and preferences, with goals and measurable objectives, the specific services and who provides them, target dates, and the person's signature. The plan is reviewed on a stated schedule and updated when things change.</t>
+          <t>If the program does not prescribe, dispense, administer, or store medication, that must be stated in writing, and staff must know their limits and what to do about medication questions and adverse reactions. If it does any of those things, a full medication management policy set is required.</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Peer Support Progress Note</t>
+          <t>Medication — What Your Peer Specialist Can and Cannot Do</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
       <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>The staff member who delivered the service</t>
+          <t>Person served</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>
@@ -5134,22 +5134,22 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Transition/Discharge</t>
+          <t>Promoting Nonviolent Practices</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Transition planning begins at admission, not at the end. There is a written transition/discharge summary for every person who leaves, including unplanned exits, and a documented attempt at follow-up after discharge with the results recorded and analyzed.</t>
+          <t>A written commitment to nonviolent practice: de-escalation training for staff, what is prohibited, what to do in a behavioral crisis, when to call for help, and a debriefing with the person served and staff after any crisis event.</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>2D-01 Transition Planning</t>
+          <t>2F-01 Nonviolent Practices</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -5176,22 +5176,22 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Transition/Discharge</t>
+          <t>Promoting Nonviolent Practices</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Transition planning begins at admission, not at the end. There is a written transition/discharge summary for every person who leaves, including unplanned exits, and a documented attempt at follow-up after discharge with the results recorded and analyzed.</t>
+          <t>A written commitment to nonviolent practice: de-escalation training for staff, what is prohibited, what to do in a behavioral crisis, when to call for help, and a debriefing with the person served and staff after any crisis event.</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>2D-02 Discharge Summary and Follow-Up</t>
+          <t>2F-02 Crisis Response and Debriefing</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr"/>
@@ -5218,22 +5218,22 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Transition/Discharge</t>
+          <t>Promoting Nonviolent Practices</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Transition planning begins at admission, not at the end. There is a written transition/discharge summary for every person who leaves, including unplanned exits, and a documented attempt at follow-up after discharge with the results recorded and analyzed.</t>
+          <t>A written commitment to nonviolent practice: de-escalation training for staff, what is prohibited, what to do in a behavioral crisis, when to call for help, and a debriefing with the person served and staff after any crisis event.</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Transition / Discharge Summary</t>
+          <t>Crisis Debriefing Form</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Peer Support Specialist and Supervisor</t>
+          <t>[FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
@@ -5260,22 +5260,22 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Transition/Discharge</t>
+          <t>Promoting Nonviolent Practices</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Transition planning begins at admission, not at the end. There is a written transition/discharge summary for every person who leaves, including unplanned exits, and a documented attempt at follow-up after discharge with the results recorded and analyzed.</t>
+          <t>A written commitment to nonviolent practice: de-escalation training for staff, what is prohibited, what to do in a behavioral crisis, when to call for help, and a debriefing with the person served and staff after any crisis event.</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Post-Discharge Follow-Up Contact Log</t>
+          <t>De-escalation and Nonviolent Practices Training Log</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -5302,22 +5302,22 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Transition/Discharge</t>
+          <t>Promoting Nonviolent Practices</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Transition planning begins at admission, not at the end. There is a written transition/discharge summary for every person who leaves, including unplanned exits, and a documented attempt at follow-up after discharge with the results recorded and analyzed.</t>
+          <t>A written commitment to nonviolent practice: de-escalation training for staff, what is prohibited, what to do in a behavioral crisis, when to call for help, and a debriefing with the person served and staff after any crisis event.</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Unplanned Exit Review</t>
+          <t>My Personal Safety and Crisis Plan</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name] with the Peer Support Specialist</t>
+          <t>The person served, with their Peer Support Specialist</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
@@ -5344,22 +5344,22 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>2.E</t>
+          <t>2.G</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Medication Use</t>
+          <t>Records of the Persons Served</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>If the program does not prescribe, dispense, administer, or store medication, that must be stated in writing, and staff must know their limits and what to do about medication questions and adverse reactions. If it does any of those things, a full medication management policy set is required.</t>
+          <t>A written list of what belongs in a record, who may write in it, how quickly entries must be made, how corrections are made, how records are secured, how long they are kept, and how they are destroyed. Entries are legible, dated, and signed with credential.</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>2E-01 Medication</t>
+          <t>2G-01 Content and Maintenance of the Record of the Person Served</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -5386,34 +5386,34 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>2.E</t>
+          <t>2.G</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Medication Use</t>
+          <t>Records of the Persons Served</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>If the program does not prescribe, dispense, administer, or store medication, that must be stated in writing, and staff must know their limits and what to do about medication questions and adverse reactions. If it does any of those things, a full medication management policy set is required.</t>
+          <t>A written list of what belongs in a record, who may write in it, how quickly entries must be made, how corrections are made, how records are secured, how long they are kept, and how they are destroyed. Entries are legible, dated, and signed with credential.</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Medication — What Your Peer Specialist Can and Cannot Do</t>
+          <t>2G-02 Records Retention, Access, and Destruction</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Person served</t>
+          <t>[FILL IN: Privacy Officer]</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
@@ -5428,34 +5428,34 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.G</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Nonviolent Practices</t>
+          <t>Records of the Persons Served</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>A written commitment to nonviolent practice: de-escalation training for staff, what is prohibited, what to do in a behavioral crisis, when to call for help, and a debriefing with the person served and staff after any crisis event.</t>
+          <t>A written list of what belongs in a record, who may write in it, how quickly entries must be made, how corrections are made, how records are secured, how long they are kept, and how they are destroyed. Entries are legible, dated, and signed with credential.</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>2F-01 Nonviolent Practices</t>
+          <t>Record Content Checklist</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Quality Improvement Coordinator] or Supervisor</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr"/>
@@ -5470,34 +5470,34 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.G</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Nonviolent Practices</t>
+          <t>Records of the Persons Served</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>A written commitment to nonviolent practice: de-escalation training for staff, what is prohibited, what to do in a behavioral crisis, when to call for help, and a debriefing with the person served and staff after any crisis event.</t>
+          <t>A written list of what belongs in a record, who may write in it, how quickly entries must be made, how corrections are made, how records are secured, how long they are kept, and how they are destroyed. Entries are legible, dated, and signed with credential.</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>2F-02 Crisis Response and Debriefing</t>
+          <t>Records Retention Schedule</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Supervisor of the peer workforce]</t>
+          <t>[FILL IN: Privacy Officer]</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr"/>
@@ -5512,34 +5512,34 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.H</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Nonviolent Practices</t>
+          <t>Quality Records Management</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>A written commitment to nonviolent practice: de-escalation training for staff, what is prohibited, what to do in a behavioral crisis, when to call for help, and a debriefing with the person served and staff after any crisis event.</t>
+          <t>Records are reviewed on a written schedule using a written tool, by someone qualified, looking at whether documentation supports the service and the plan. Results are aggregated, trends identified, and corrective action tracked to closure.</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Crisis Debriefing Form</t>
+          <t>2H-01 Quality Record Review</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Supervisor of the peer workforce]</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr"/>
@@ -5554,22 +5554,22 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.H</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Nonviolent Practices</t>
+          <t>Quality Records Management</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>A written commitment to nonviolent practice: de-escalation training for staff, what is prohibited, what to do in a behavioral crisis, when to call for help, and a debriefing with the person served and staff after any crisis event.</t>
+          <t>Records are reviewed on a written schedule using a written tool, by someone qualified, looking at whether documentation supports the service and the plan. Results are aggregated, trends identified, and corrective action tracked to closure.</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>De-escalation and Nonviolent Practices Training Log</t>
+          <t>Quality Record Review Tool</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -5581,7 +5581,7 @@
       <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Quality Improvement Coordinator] or qualified designee who did not write the documentation</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr"/>
@@ -5596,22 +5596,22 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.H</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Nonviolent Practices</t>
+          <t>Quality Records Management</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>A written commitment to nonviolent practice: de-escalation training for staff, what is prohibited, what to do in a behavioral crisis, when to call for help, and a debriefing with the person served and staff after any crisis event.</t>
+          <t>Records are reviewed on a written schedule using a written tool, by someone qualified, looking at whether documentation supports the service and the plan. Results are aggregated, trends identified, and corrective action tracked to closure.</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>My Personal Safety and Crisis Plan</t>
+          <t>Quarterly Record Review Summary Report</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>The person served, with their Peer Support Specialist</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr"/>
@@ -5638,34 +5638,34 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>2.G</t>
+          <t>2.H</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Records of the Persons Served</t>
+          <t>Quality Records Management</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>A written list of what belongs in a record, who may write in it, how quickly entries must be made, how corrections are made, how records are secured, how long they are kept, and how they are destroyed. Entries are legible, dated, and signed with credential.</t>
+          <t>Records are reviewed on a written schedule using a written tool, by someone qualified, looking at whether documentation supports the service and the plan. Results are aggregated, trends identified, and corrective action tracked to closure.</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>2G-01 Content and Maintenance of the Record of the Person Served</t>
+          <t>Corrective Action Tracker</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Quality Improvement Coordinator]</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr"/>
@@ -5680,22 +5680,22 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>2.G</t>
+          <t>2.I</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Records of the Persons Served</t>
+          <t>Service Delivery Using Information and Communication Technologies</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>A written list of what belongs in a record, who may write in it, how quickly entries must be made, how corrections are made, how records are secured, how long they are kept, and how they are destroyed. Entries are legible, dated, and signed with credential.</t>
+          <t>Where any part of the service is delivered by video, phone or other technology, it meets the same standards as in-person service: informed consent specific to the technology, identity and location verified at each contact, an emergency plan for the person's actual location, an approved platform under a business associate agreement, staff trained and assessed as competent in delivering peer support remotely, and documentation that records the modality and both parties' locations.</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>2G-02 Records Retention, Access, and Destruction</t>
+          <t>2I-01 Information and Communication Technology in Service Delivery (Telehealth)</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -5707,7 +5707,7 @@
       <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Privacy Officer]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr"/>
@@ -5722,34 +5722,34 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>2.G</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Records of the Persons Served</t>
+          <t>Community Integration</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>A written list of what belongs in a record, who may write in it, how quickly entries must be made, how corrections are made, how records are secured, how long they are kept, and how they are destroyed. Entries are legible, dated, and signed with credential.</t>
+          <t>The program helps people participate in community life as they choose - housing, work, education, benefits, relationships, transportation, recreation, health care, and civic life. It is built on the person's own goals, uses natural supports and real community settings rather than segregated ones, and measures actual community participation, not just service contacts.</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Record Content Checklist</t>
+          <t>3C-01 Community Integration Program Philosophy and Scope</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator] or Supervisor</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr"/>
@@ -5764,34 +5764,34 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>2.G</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Records of the Persons Served</t>
+          <t>Community Integration</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>A written list of what belongs in a record, who may write in it, how quickly entries must be made, how corrections are made, how records are secured, how long they are kept, and how they are destroyed. Entries are legible, dated, and signed with credential.</t>
+          <t>The program helps people participate in community life as they choose - housing, work, education, benefits, relationships, transportation, recreation, health care, and civic life. It is built on the person's own goals, uses natural supports and real community settings rather than segregated ones, and measures actual community participation, not just service contacts.</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Records Retention Schedule</t>
+          <t>3C-02 Choice, Self-Determination, and Dignity of Risk</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Privacy Officer]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr"/>
@@ -5806,22 +5806,22 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>2.H</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Quality Record Review</t>
+          <t>Community Integration</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Records are reviewed on a written schedule using a written tool, by someone qualified, looking at whether documentation supports the service and the plan. Results are aggregated, trends identified, and corrective action tracked to closure.</t>
+          <t>The program helps people participate in community life as they choose - housing, work, education, benefits, relationships, transportation, recreation, health care, and civic life. It is built on the person's own goals, uses natural supports and real community settings rather than segregated ones, and measures actual community participation, not just service contacts.</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>2H-01 Quality Record Review</t>
+          <t>3C-03 Natural Supports and Community Connection</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -5833,7 +5833,7 @@
       <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr"/>
@@ -5848,34 +5848,34 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>2.H</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Quality Record Review</t>
+          <t>Community Integration</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Records are reviewed on a written schedule using a written tool, by someone qualified, looking at whether documentation supports the service and the plan. Results are aggregated, trends identified, and corrective action tracked to closure.</t>
+          <t>The program helps people participate in community life as they choose - housing, work, education, benefits, relationships, transportation, recreation, health care, and civic life. It is built on the person's own goals, uses natural supports and real community settings rather than segregated ones, and measures actual community participation, not just service contacts.</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Quality Record Review Tool</t>
+          <t>3C-04 Transportation and Community Outings</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator] or qualified designee who did not write the documentation</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr"/>
@@ -5890,34 +5890,34 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>2.H</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Quality Record Review</t>
+          <t>Community Integration</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Records are reviewed on a written schedule using a written tool, by someone qualified, looking at whether documentation supports the service and the plan. Results are aggregated, trends identified, and corrective action tracked to closure.</t>
+          <t>The program helps people participate in community life as they choose - housing, work, education, benefits, relationships, transportation, recreation, health care, and civic life. It is built on the person's own goals, uses natural supports and real community settings rather than segregated ones, and measures actual community participation, not just service contacts.</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Quarterly Record Review Summary Report</t>
+          <t>3C-05 Advocacy, Benefits, and Removing Barriers</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr"/>
@@ -5932,22 +5932,22 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>2.H</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Quality Record Review</t>
+          <t>Community Integration</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Records are reviewed on a written schedule using a written tool, by someone qualified, looking at whether documentation supports the service and the plan. Results are aggregated, trends identified, and corrective action tracked to closure.</t>
+          <t>The program helps people participate in community life as they choose - housing, work, education, benefits, relationships, transportation, recreation, health care, and civic life. It is built on the person's own goals, uses natural supports and real community settings rather than segregated ones, and measures actual community participation, not just service contacts.</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Corrective Action Tracker</t>
+          <t>Community Integration Goal Worksheet</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -5959,7 +5959,7 @@
       <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Quality Improvement Coordinator]</t>
+          <t>The person served with their Peer Support Specialist</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr"/>
@@ -5974,7 +5974,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -5989,19 +5989,19 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>3CI-01 Community Integration Program Philosophy and Scope</t>
+          <t>Natural Supports Map</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>The person served with their Peer Support Specialist</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr"/>
@@ -6016,7 +6016,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>3CI-02 Choice, Self-Determination, and Dignity of Risk</t>
+          <t>Community Resource Directory</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr"/>
@@ -6058,7 +6058,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6073,19 +6073,19 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>3CI-03 Natural Supports and Community Connection</t>
+          <t>Benefits and Entitlements Checklist</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>The person served with their Peer Support Specialist</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr"/>
@@ -6100,22 +6100,22 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.PEER</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Community Integration</t>
+          <t>Peer Workforce Requirements (this skill's own grouping - NOT a CARF area)</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>The program helps people participate in community life as they choose - housing, work, education, benefits, relationships, transportation, recreation, health care, and civic life. It is built on the person's own goals, uses natural supports and real community settings rather than segregated ones, and measures actual community participation, not just service contacts.</t>
+          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder. CONFIRMED against the 2026 table of contents: there is no Peer Support program in Sections 3 or 4, and CARF's own 2026 Behavioral Health Program Descriptions mention peer support once in 23 pages, as staffing for a crisis contact center. The nearest real CARF home for this material is the CONSUMER-RUN specialty designation at 5.D, page 318 - check whether the agency qualifies.</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>3CI-04 Transportation and Community Outings</t>
+          <t>3P-01 The Peer Support Service Model</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -6142,22 +6142,22 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.PEER</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Community Integration</t>
+          <t>Peer Workforce Requirements (this skill's own grouping - NOT a CARF area)</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>The program helps people participate in community life as they choose - housing, work, education, benefits, relationships, transportation, recreation, health care, and civic life. It is built on the person's own goals, uses natural supports and real community settings rather than segregated ones, and measures actual community participation, not just service contacts.</t>
+          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder. CONFIRMED against the 2026 table of contents: there is no Peer Support program in Sections 3 or 4, and CARF's own 2026 Behavioral Health Program Descriptions mention peer support once in 23 pages, as staffing for a crisis contact center. The nearest real CARF home for this material is the CONSUMER-RUN specialty designation at 5.D, page 318 - check whether the agency qualifies.</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>3CI-05 Advocacy, Benefits, and Removing Barriers</t>
+          <t>3P-02 Self-Disclosure</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr"/>
@@ -6184,34 +6184,34 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.PEER</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Community Integration</t>
+          <t>Peer Workforce Requirements (this skill's own grouping - NOT a CARF area)</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>The program helps people participate in community life as they choose - housing, work, education, benefits, relationships, transportation, recreation, health care, and civic life. It is built on the person's own goals, uses natural supports and real community settings rather than segregated ones, and measures actual community participation, not just service contacts.</t>
+          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder. CONFIRMED against the 2026 table of contents: there is no Peer Support program in Sections 3 or 4, and CARF's own 2026 Behavioral Health Program Descriptions mention peer support once in 23 pages, as staffing for a crisis contact center. The nearest real CARF home for this material is the CONSUMER-RUN specialty designation at 5.D, page 318 - check whether the agency qualifies.</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Community Integration Goal Worksheet</t>
+          <t>3P-03 Boundaries and Dual Relationships</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>The person served with their Peer Support Specialist</t>
+          <t>[FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr"/>
@@ -6226,34 +6226,34 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.PEER</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Community Integration</t>
+          <t>Peer Workforce Requirements (this skill's own grouping - NOT a CARF area)</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>The program helps people participate in community life as they choose - housing, work, education, benefits, relationships, transportation, recreation, health care, and civic life. It is built on the person's own goals, uses natural supports and real community settings rather than segregated ones, and measures actual community participation, not just service contacts.</t>
+          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder. CONFIRMED against the 2026 table of contents: there is no Peer Support program in Sections 3 or 4, and CARF's own 2026 Behavioral Health Program Descriptions mention peer support once in 23 pages, as staffing for a crisis contact center. The nearest real CARF home for this material is the CONSUMER-RUN specialty designation at 5.D, page 318 - check whether the agency qualifies.</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Natural Supports Map</t>
+          <t>3P-04 Peer Workforce Wellness</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>The person served with their Peer Support Specialist</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr"/>
@@ -6268,34 +6268,34 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.PEER</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Community Integration</t>
+          <t>Peer Workforce Requirements (this skill's own grouping - NOT a CARF area)</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>The program helps people participate in community life as they choose - housing, work, education, benefits, relationships, transportation, recreation, health care, and civic life. It is built on the person's own goals, uses natural supports and real community settings rather than segregated ones, and measures actual community participation, not just service contacts.</t>
+          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder. CONFIRMED against the 2026 table of contents: there is no Peer Support program in Sections 3 or 4, and CARF's own 2026 Behavioral Health Program Descriptions mention peer support once in 23 pages, as staffing for a crisis contact center. The nearest real CARF home for this material is the CONSUMER-RUN specialty designation at 5.D, page 318 - check whether the agency qualifies.</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Community Resource Directory</t>
+          <t>3P-05 Peer Specialist Credential, Scope, and Career Ladder</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr"/>
@@ -6310,22 +6310,22 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.PEER</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Community Integration</t>
+          <t>Peer Workforce Requirements (this skill's own grouping - NOT a CARF area)</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>The program helps people participate in community life as they choose - housing, work, education, benefits, relationships, transportation, recreation, health care, and civic life. It is built on the person's own goals, uses natural supports and real community settings rather than segregated ones, and measures actual community participation, not just service contacts.</t>
+          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder. CONFIRMED against the 2026 table of contents: there is no Peer Support program in Sections 3 or 4, and CARF's own 2026 Behavioral Health Program Descriptions mention peer support once in 23 pages, as staffing for a crisis contact center. The nearest real CARF home for this material is the CONSUMER-RUN specialty designation at 5.D, page 318 - check whether the agency qualifies.</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Benefits and Entitlements Checklist</t>
+          <t>Job Description — Peer Support Specialist</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -6337,7 +6337,7 @@
       <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>The person served with their Peer Support Specialist</t>
+          <t>Employee and supervisor sign at hire and at revision</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr"/>
@@ -6357,29 +6357,29 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Peer Workforce Requirements (cross-cutting)</t>
+          <t>Peer Workforce Requirements (this skill's own grouping - NOT a CARF area)</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder.</t>
+          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder. CONFIRMED against the 2026 table of contents: there is no Peer Support program in Sections 3 or 4, and CARF's own 2026 Behavioral Health Program Descriptions mention peer support once in 23 pages, as staffing for a crisis contact center. The nearest real CARF home for this material is the CONSUMER-RUN specialty designation at 5.D, page 318 - check whether the agency qualifies.</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>3P-01 The Peer Support Service Model</t>
+          <t>Competency Assessment — Peer Support Specialist</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr"/>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Program Director name]</t>
+          <t>[FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr"/>
@@ -6399,29 +6399,29 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Peer Workforce Requirements (cross-cutting)</t>
+          <t>Peer Workforce Requirements (this skill's own grouping - NOT a CARF area)</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder.</t>
+          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder. CONFIRMED against the 2026 table of contents: there is no Peer Support program in Sections 3 or 4, and CARF's own 2026 Behavioral Health Program Descriptions mention peer support once in 23 pages, as staffing for a crisis contact center. The nearest real CARF home for this material is the CONSUMER-RUN specialty designation at 5.D, page 318 - check whether the agency qualifies.</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>3P-02 Self-Disclosure</t>
+          <t>Self-Disclosure Supervision Worksheet</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Supervisor of the peer workforce]</t>
+          <t>Peer Support Specialist with [FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr"/>
@@ -6441,29 +6441,29 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Peer Workforce Requirements (cross-cutting)</t>
+          <t>Peer Workforce Requirements (this skill's own grouping - NOT a CARF area)</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder.</t>
+          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder. CONFIRMED against the 2026 table of contents: there is no Peer Support program in Sections 3 or 4, and CARF's own 2026 Behavioral Health Program Descriptions mention peer support once in 23 pages, as staffing for a crisis contact center. The nearest real CARF home for this material is the CONSUMER-RUN specialty designation at 5.D, page 318 - check whether the agency qualifies.</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>3P-03 Boundaries and Dual Relationships</t>
+          <t>Dual Relationship Disclosure and Management Plan</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr"/>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Supervisor of the peer workforce]</t>
+          <t>Any staff member; management plan by [FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr"/>
@@ -6483,29 +6483,29 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Peer Workforce Requirements (cross-cutting)</t>
+          <t>Peer Workforce Requirements (this skill's own grouping - NOT a CARF area)</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder.</t>
+          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder. CONFIRMED against the 2026 table of contents: there is no Peer Support program in Sections 3 or 4, and CARF's own 2026 Behavioral Health Program Descriptions mention peer support once in 23 pages, as staffing for a crisis contact center. The nearest real CARF home for this material is the CONSUMER-RUN specialty designation at 5.D, page 318 - check whether the agency qualifies.</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>3P-04 Peer Workforce Wellness</t>
+          <t>My Peer Wellness Plan (Staff)</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Form / evidence</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Peer Support Specialist with [FILL IN: Supervisor of the peer workforce]</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr"/>
@@ -6520,22 +6520,22 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Peer Workforce Requirements (cross-cutting)</t>
+          <t>Technology and Information Security - CARF home NOT YET CONFIRMED</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder.</t>
+          <t>The 2026 Section 1 has NO Technology area - it runs A Leadership to M Performance Improvement with no technology heading. These three policies (technology and system planning, information security, and social media / devices / electronic communication) are good practice and most payers require them, but their home in the manual is unconfirmed. Service delivery BY technology is a different thing and lives at 2.I. FIND THEIR HOME IN APPENDIX A (Required Written Documentation, page 385), which lists every document the manual requires, and move them to whichever area it names.</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>3P-05 Peer Specialist Credential, Scope, and Career Ladder</t>
+          <t>TECH-01 Technology and System Planning</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -6562,34 +6562,34 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Peer Workforce Requirements (cross-cutting)</t>
+          <t>Technology and Information Security - CARF home NOT YET CONFIRMED</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder.</t>
+          <t>The 2026 Section 1 has NO Technology area - it runs A Leadership to M Performance Improvement with no technology heading. These three policies (technology and system planning, information security, and social media / devices / electronic communication) are good practice and most payers require them, but their home in the manual is unconfirmed. Service delivery BY technology is a different thing and lives at 2.I. FIND THEIR HOME IN APPENDIX A (Required Written Documentation, page 385), which lists every document the manual requires, and move them to whichever area it names.</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Job Description — Peer Support Specialist</t>
+          <t>TECH-02 Information Security and Confidentiality of Data</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Employee and supervisor sign at hire and at revision</t>
+          <t>[FILL IN: Privacy Officer]</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr"/>
@@ -6604,34 +6604,34 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Peer Workforce Requirements (cross-cutting)</t>
+          <t>Technology and Information Security - CARF home NOT YET CONFIRMED</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder.</t>
+          <t>The 2026 Section 1 has NO Technology area - it runs A Leadership to M Performance Improvement with no technology heading. These three policies (technology and system planning, information security, and social media / devices / electronic communication) are good practice and most payers require them, but their home in the manual is unconfirmed. Service delivery BY technology is a different thing and lives at 2.I. FIND THEIR HOME IN APPENDIX A (Required Written Documentation, page 385), which lists every document the manual requires, and move them to whichever area it names.</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Competency Assessment — Peer Support Specialist</t>
+          <t>TECH-03 Social Media, Mobile Devices, and Electronic Communication</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr"/>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>[FILL IN: Supervisor of the peer workforce]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr"/>
@@ -6646,34 +6646,34 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Peer Workforce Requirements (cross-cutting)</t>
+          <t>Technology and Information Security - CARF home NOT YET CONFIRMED</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder.</t>
+          <t>The 2026 Section 1 has NO Technology area - it runs A Leadership to M Performance Improvement with no technology heading. These three policies (technology and system planning, information security, and social media / devices / electronic communication) are good practice and most payers require them, but their home in the manual is unconfirmed. Service delivery BY technology is a different thing and lives at 2.I. FIND THEIR HOME IN APPENDIX A (Required Written Documentation, page 385), which lists every document the manual requires, and move them to whichever area it names.</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Self-Disclosure Supervision Worksheet</t>
+          <t>2I-01 Information and Communication Technology in Service Delivery (Telehealth)</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr"/>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>Peer Support Specialist with [FILL IN: Supervisor of the peer workforce]</t>
+          <t>[FILL IN: Program Director name]</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr"/>
@@ -6688,34 +6688,34 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Peer Workforce Requirements (cross-cutting)</t>
+          <t>Technology and Information Security - CARF home NOT YET CONFIRMED</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder.</t>
+          <t>The 2026 Section 1 has NO Technology area - it runs A Leadership to M Performance Improvement with no technology heading. These three policies (technology and system planning, information security, and social media / devices / electronic communication) are good practice and most payers require them, but their home in the manual is unconfirmed. Service delivery BY technology is a different thing and lives at 2.I. FIND THEIR HOME IN APPENDIX A (Required Written Documentation, page 385), which lists every document the manual requires, and move them to whichever area it names.</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Dual Relationship Disclosure and Management Plan</t>
+          <t>Technology and System Plan</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Form / evidence</t>
+          <t>Written plan</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr"/>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>Any staff member; management plan by [FILL IN: Supervisor of the peer workforce]</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr"/>
@@ -6730,22 +6730,22 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>X.TECH</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Peer Workforce Requirements (cross-cutting)</t>
+          <t>Technology and Information Security - CARF home NOT YET CONFIRMED</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Peer support is a WORKFORCE and a service model, not a separate CARF program section. Its requirements are enforced through 1.I (credential, competency, supervision), 2.A (program description and staffing), 2.C (person-centered planning done WITH the person), and the Section 3 program. This area exists so nothing peer-specific falls between the cracks: lived experience as a job qualification, the state peer credential, self-disclosure boundaries, mutuality, dual-relationship management in small recovery communities, peer staff wellness, and career ladder.</t>
+          <t>The 2026 Section 1 has NO Technology area - it runs A Leadership to M Performance Improvement with no technology heading. These three policies (technology and system planning, information security, and social media / devices / electronic communication) are good practice and most payers require them, but their home in the manual is unconfirmed. Service delivery BY technology is a different thing and lives at 2.I. FIND THEIR HOME IN APPENDIX A (Required Written Documentation, page 385), which lists every document the manual requires, and move them to whichever area it names.</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>My Peer Wellness Plan (Staff)</t>
+          <t>System Downtime Service Log and Procedure</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       <c r="G150" s="2" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Peer Support Specialist with [FILL IN: Supervisor of the peer workforce]</t>
+          <t>All staff</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr"/>
@@ -6769,8 +6769,50 @@
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>X.TECH</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Technology and Information Security - CARF home NOT YET CONFIRMED</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>The 2026 Section 1 has NO Technology area - it runs A Leadership to M Performance Improvement with no technology heading. These three policies (technology and system planning, information security, and social media / devices / electronic communication) are good practice and most payers require them, but their home in the manual is unconfirmed. Service delivery BY technology is a different thing and lives at 2.I. FIND THEIR HOME IN APPENDIX A (Required Written Documentation, page 385), which lists every document the manual requires, and move them to whichever area it names.</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Device and System Access Log</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Form / evidence</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>[FILL IN: Privacy Officer]</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L150"/>
+  <autoFilter ref="A1:L151"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6781,7 +6823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7396,12 +7438,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CEO, Privacy Officer, Direct staff</t>
+          <t>Persons served, Direct staff, Privacy Officer</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>What happens to service delivery if your EHR is down for two days?</t>
+          <t>Ask a person served: do you know how to file a complaint?</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
@@ -7415,12 +7457,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CEO, Privacy Officer, Direct staff</t>
+          <t>Persons served, Direct staff, Privacy Officer</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>When did you last test a restore from backup?</t>
+          <t>Show me the grievance log and what happened with each one.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
@@ -7434,12 +7476,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CEO, Privacy Officer, Direct staff</t>
+          <t>Persons served, Direct staff, Privacy Officer</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Show me your texting and social media rules for peer staff.</t>
+          <t>Show me signed consents in three records.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
@@ -7453,12 +7495,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Persons served, Direct staff, Privacy Officer</t>
+          <t>CEO, Persons served, Direct staff</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Ask a person served: do you know how to file a complaint?</t>
+          <t>Show me your accessibility plan and this year's progress.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
@@ -7472,12 +7514,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Persons served, Direct staff, Privacy Officer</t>
+          <t>CEO, Persons served, Direct staff</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Show me the grievance log and what happened with each one.</t>
+          <t>What barrier did you remove in the last twelve months?</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
@@ -7491,12 +7533,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Persons served, Direct staff, Privacy Officer</t>
+          <t>CEO, Persons served, Direct staff</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Show me signed consents in three records.</t>
+          <t>How would a person who is deaf access your service?</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
@@ -7510,12 +7552,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>CEO, Persons served, Direct staff</t>
+          <t>QI Coordinator, CEO, Program Director</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Show me your accessibility plan and this year's progress.</t>
+          <t>What exactly do you measure and what is your target?</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
@@ -7529,12 +7571,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>CEO, Persons served, Direct staff</t>
+          <t>QI Coordinator, CEO, Program Director</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>What barrier did you remove in the last twelve months?</t>
+          <t>Show me the data for the last four quarters.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
@@ -7548,12 +7590,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>CEO, Persons served, Direct staff</t>
+          <t>QI Coordinator, CEO, Program Director</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>How would a person who is deaf access your service?</t>
+          <t>How do you define a successful outcome for a person in peer support?</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
@@ -7567,12 +7609,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>QI Coordinator, CEO, Program Director</t>
+          <t>QI Coordinator, CEO, Direct staff, Persons served</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>What exactly do you measure and what is your target?</t>
+          <t>Show me last year's written performance analysis.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
@@ -7586,12 +7628,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>QI Coordinator, CEO, Program Director</t>
+          <t>QI Coordinator, CEO, Direct staff, Persons served</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Show me the data for the last four quarters.</t>
+          <t>Name one improvement project and show me the before and after numbers.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -7605,12 +7647,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>QI Coordinator, CEO, Program Director</t>
+          <t>QI Coordinator, CEO, Direct staff, Persons served</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>How do you define a successful outcome for a person in peer support?</t>
+          <t>How did the people you serve find out about these results?</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -7619,17 +7661,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>QI Coordinator, CEO, Direct staff, Persons served</t>
+          <t>Program Director, Direct staff</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Show me last year's written performance analysis.</t>
+          <t>Show me the written program description.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -7638,17 +7680,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>QI Coordinator, CEO, Direct staff, Persons served</t>
+          <t>Program Director, Direct staff</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Name one improvement project and show me the before and after numbers.</t>
+          <t>Does what I am seeing on site match what this says?</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -7657,17 +7699,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>1.N</t>
+          <t>2.A</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>QI Coordinator, CEO, Direct staff, Persons served</t>
+          <t>Program Director, Direct staff</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>How did the people you serve find out about these results?</t>
+          <t>How many people can one peer specialist carry, and how did you decide that?</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -7676,17 +7718,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Program Director, Direct staff</t>
+          <t>Program Director, Direct staff, Persons served</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Show me the written program description.</t>
+          <t>How long between the referral and the first contact? Prove it.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -7695,17 +7737,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Program Director, Direct staff</t>
+          <t>Program Director, Direct staff, Persons served</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Does what I am seeing on site match what this says?</t>
+          <t>Show me a signed orientation checklist in a record.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -7714,17 +7756,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2.A</t>
+          <t>2.B</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Program Director, Direct staff</t>
+          <t>Program Director, Direct staff, Persons served</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>How many people can one peer specialist carry, and how did you decide that?</t>
+          <t>What do you do when someone does not meet criteria?</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -7733,17 +7775,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Program Director, Direct staff, Persons served</t>
+          <t>Persons served, Direct staff, Supervisor</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>How long between the referral and the first contact? Prove it.</t>
+          <t>Read me a goal in the person's own words.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -7752,17 +7794,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Program Director, Direct staff, Persons served</t>
+          <t>Persons served, Direct staff, Supervisor</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Show me a signed orientation checklist in a record.</t>
+          <t>Show me where the person signed and dated the plan.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -7771,17 +7813,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2.B</t>
+          <t>2.C</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Program Director, Direct staff, Persons served</t>
+          <t>Persons served, Direct staff, Supervisor</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>What do you do when someone does not meet criteria?</t>
+          <t>Show me the review that was due last month.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -7800,7 +7842,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Read me a goal in the person's own words.</t>
+          <t>Does this progress note connect to a goal on this plan?</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -7809,17 +7851,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Persons served, Direct staff, Supervisor</t>
+          <t>Program Director, Direct staff</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Show me where the person signed and dated the plan.</t>
+          <t>Show me discharge summaries for the last five people who left, including the ones who just stopped coming.</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
@@ -7828,17 +7870,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.D</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Persons served, Direct staff, Supervisor</t>
+          <t>Program Director, Direct staff</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Show me the review that was due last month.</t>
+          <t>What does your follow-up data tell you?</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
@@ -7847,17 +7889,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2.C</t>
+          <t>2.E</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Persons served, Direct staff, Supervisor</t>
+          <t>Program Director, Direct staff</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Does this progress note connect to a goal on this plan?</t>
+          <t>Do you touch medication in any way?</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -7866,7 +7908,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.E</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -7876,7 +7918,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Show me discharge summaries for the last five people who left, including the ones who just stopped coming.</t>
+          <t>Ask a peer specialist: what do you do if someone tells you they stopped their medication?</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
@@ -7885,17 +7927,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2.D</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Program Director, Direct staff</t>
+          <t>Direct staff, Supervisor, Persons served</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>What does your follow-up data tell you?</t>
+          <t>What restraint or seclusion do you use? (correct answer for most peer programs: none, and it is prohibited in writing)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
@@ -7904,17 +7946,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2.E</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Program Director, Direct staff</t>
+          <t>Direct staff, Supervisor, Persons served</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Do you touch medication in any way?</t>
+          <t>Ask staff: what do you do if someone escalates in the car?</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
@@ -7923,17 +7965,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2.E</t>
+          <t>2.F</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Program Director, Direct staff</t>
+          <t>Direct staff, Supervisor, Persons served</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Ask a peer specialist: what do you do if someone tells you they stopped their medication?</t>
+          <t>Show me a debriefing after your last crisis event.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
@@ -7942,17 +7984,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.G</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Direct staff, Supervisor, Persons served</t>
+          <t>Program Director, Direct staff, Records custodian</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>What restraint or seclusion do you use? (correct answer for most peer programs: none, and it is prohibited in writing)</t>
+          <t>What is your documentation timeframe and can you prove notes meet it?</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
@@ -7961,17 +8003,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.G</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Direct staff, Supervisor, Persons served</t>
+          <t>Program Director, Direct staff, Records custodian</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Ask staff: what do you do if someone escalates in the car?</t>
+          <t>Where are paper records kept and who has the key?</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
@@ -7980,17 +8022,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>2.F</t>
+          <t>2.G</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Direct staff, Supervisor, Persons served</t>
+          <t>Program Director, Direct staff, Records custodian</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Show me a debriefing after your last crisis event.</t>
+          <t>Show me how a correction is made.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
@@ -7999,17 +8041,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2.G</t>
+          <t>2.H</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Program Director, Direct staff, Records custodian</t>
+          <t>QI Coordinator, Supervisor</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>What is your documentation timeframe and can you prove notes meet it?</t>
+          <t>Show me your last four quarterly record reviews.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
@@ -8018,17 +8060,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>2.G</t>
+          <t>2.H</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Program Director, Direct staff, Records custodian</t>
+          <t>QI Coordinator, Supervisor</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Where are paper records kept and who has the key?</t>
+          <t>What did you find and what did you do about it?</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
@@ -8037,17 +8079,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2.G</t>
+          <t>2.H</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Program Director, Direct staff, Records custodian</t>
+          <t>QI Coordinator, Supervisor</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Show me how a correction is made.</t>
+          <t>Show me that the correction actually happened.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -8056,17 +8098,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>2.H</t>
+          <t>2.I</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>QI Coordinator, Supervisor</t>
+          <t>Program Director, Direct staff, Persons served</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Show me your last four quarterly record reviews.</t>
+          <t>Do you deliver any part of this service by video or phone?</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -8075,17 +8117,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2.H</t>
+          <t>2.I</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>QI Coordinator, Supervisor</t>
+          <t>Program Director, Direct staff, Persons served</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>What did you find and what did you do about it?</t>
+          <t>Show me a technology-specific consent.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
@@ -8094,17 +8136,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>2.H</t>
+          <t>2.I</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>QI Coordinator, Supervisor</t>
+          <t>Program Director, Direct staff, Persons served</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Show me that the correction actually happened.</t>
+          <t>Where is the person when you meet by video, and how do you know?</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
@@ -8113,17 +8155,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>2.I</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Persons served, Direct staff, Program Director</t>
+          <t>Program Director, Direct staff, Persons served</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Show me a person who moved into their own housing, got a job, or joined something in the community because of you.</t>
+          <t>If someone was in crisis on a video call, how would you get help to them?</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
@@ -8132,7 +8174,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -8142,7 +8184,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>How do you measure community participation?</t>
+          <t>Show me a person who moved into their own housing, got a job, or joined something in the community because of you.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
@@ -8151,7 +8193,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>3.CI</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -8161,7 +8203,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Ask a person served: what do you want that we are helping you get?</t>
+          <t>How do you measure community participation?</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
@@ -8170,17 +8212,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>3.PEER</t>
+          <t>3.C</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Peer Support Specialists, Supervisor, Program Director</t>
+          <t>Persons served, Direct staff, Program Director</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>What makes someone qualified to be a peer specialist here?</t>
+          <t>Ask a person served: what do you want that we are helping you get?</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
@@ -8199,7 +8241,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>How do you supervise self-disclosure?</t>
+          <t>What makes someone qualified to be a peer specialist here?</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
@@ -8218,7 +8260,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>What happens when a peer specialist knows a participant from their own recovery community?</t>
+          <t>How do you supervise self-disclosure?</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
@@ -8237,11 +8279,87 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>How do you protect the wellness of staff in recovery?</t>
+          <t>What happens when a peer specialist knows a participant from their own recovery community?</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>3.PEER</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Peer Support Specialists, Supervisor, Program Director</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>How do you protect the wellness of staff in recovery?</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>X.TECH</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>CEO, Privacy Officer, Direct staff</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>What happens to service delivery if your EHR is down for two days?</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>X.TECH</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>CEO, Privacy Officer, Direct staff</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>When did you last test a restore from backup?</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>X.TECH</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>CEO, Privacy Officer, Direct staff</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Show me your texting and social media rules for peer staff.</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
